--- a/data-raw/resultados_supersete.xlsx
+++ b/data-raw/resultados_supersete.xlsx
@@ -355,7 +355,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E5713"/>
+  <dimension ref="A1:E5720"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" style="2" customWidth="1"/>
@@ -97492,6 +97492,125 @@
         <v>0</v>
       </c>
     </row>
+    <row r="5714">
+      <c r="A5714" s="2">
+        <v>46083</v>
+      </c>
+      <c r="B5714">
+        <v>817</v>
+      </c>
+      <c r="C5714">
+        <v>0</v>
+      </c>
+      <c r="D5714">
+        <v>0</v>
+      </c>
+      <c r="E5714">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5715">
+      <c r="A5715" s="2">
+        <v>46083</v>
+      </c>
+      <c r="B5715">
+        <v>817</v>
+      </c>
+      <c r="C5715">
+        <v>0</v>
+      </c>
+      <c r="D5715">
+        <v>0</v>
+      </c>
+      <c r="E5715">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="5716">
+      <c r="A5716" s="2">
+        <v>46083</v>
+      </c>
+      <c r="B5716">
+        <v>817</v>
+      </c>
+      <c r="C5716">
+        <v>0</v>
+      </c>
+      <c r="D5716">
+        <v>0</v>
+      </c>
+      <c r="E5716">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5717">
+      <c r="A5717" s="2">
+        <v>46083</v>
+      </c>
+      <c r="B5717">
+        <v>817</v>
+      </c>
+      <c r="C5717">
+        <v>0</v>
+      </c>
+      <c r="D5717">
+        <v>0</v>
+      </c>
+      <c r="E5717">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5718">
+      <c r="A5718" s="2">
+        <v>46083</v>
+      </c>
+      <c r="B5718">
+        <v>817</v>
+      </c>
+      <c r="C5718">
+        <v>0</v>
+      </c>
+      <c r="D5718">
+        <v>0</v>
+      </c>
+      <c r="E5718">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5719">
+      <c r="A5719" s="2">
+        <v>46083</v>
+      </c>
+      <c r="B5719">
+        <v>817</v>
+      </c>
+      <c r="C5719">
+        <v>0</v>
+      </c>
+      <c r="D5719">
+        <v>0</v>
+      </c>
+      <c r="E5719">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5720">
+      <c r="A5720" s="2">
+        <v>46083</v>
+      </c>
+      <c r="B5720">
+        <v>817</v>
+      </c>
+      <c r="C5720">
+        <v>0</v>
+      </c>
+      <c r="D5720">
+        <v>0</v>
+      </c>
+      <c r="E5720">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data-raw/resultados_supersete.xlsx
+++ b/data-raw/resultados_supersete.xlsx
@@ -355,7 +355,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E5720"/>
+  <dimension ref="A1:E5727"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" style="2" customWidth="1"/>
@@ -97611,6 +97611,125 @@
         <v>7</v>
       </c>
     </row>
+    <row r="5721">
+      <c r="A5721" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B5721">
+        <v>818</v>
+      </c>
+      <c r="C5721">
+        <v>0</v>
+      </c>
+      <c r="D5721">
+        <v>0</v>
+      </c>
+      <c r="E5721">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5722">
+      <c r="A5722" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B5722">
+        <v>818</v>
+      </c>
+      <c r="C5722">
+        <v>0</v>
+      </c>
+      <c r="D5722">
+        <v>0</v>
+      </c>
+      <c r="E5722">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5723">
+      <c r="A5723" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B5723">
+        <v>818</v>
+      </c>
+      <c r="C5723">
+        <v>0</v>
+      </c>
+      <c r="D5723">
+        <v>0</v>
+      </c>
+      <c r="E5723">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5724">
+      <c r="A5724" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B5724">
+        <v>818</v>
+      </c>
+      <c r="C5724">
+        <v>0</v>
+      </c>
+      <c r="D5724">
+        <v>0</v>
+      </c>
+      <c r="E5724">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5725">
+      <c r="A5725" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B5725">
+        <v>818</v>
+      </c>
+      <c r="C5725">
+        <v>0</v>
+      </c>
+      <c r="D5725">
+        <v>0</v>
+      </c>
+      <c r="E5725">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5726">
+      <c r="A5726" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B5726">
+        <v>818</v>
+      </c>
+      <c r="C5726">
+        <v>0</v>
+      </c>
+      <c r="D5726">
+        <v>0</v>
+      </c>
+      <c r="E5726">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5727">
+      <c r="A5727" s="2">
+        <v>46085</v>
+      </c>
+      <c r="B5727">
+        <v>818</v>
+      </c>
+      <c r="C5727">
+        <v>0</v>
+      </c>
+      <c r="D5727">
+        <v>0</v>
+      </c>
+      <c r="E5727">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data-raw/resultados_supersete.xlsx
+++ b/data-raw/resultados_supersete.xlsx
@@ -355,7 +355,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E5727"/>
+  <dimension ref="A1:E5734"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" style="2" customWidth="1"/>
@@ -97730,6 +97730,125 @@
         <v>9</v>
       </c>
     </row>
+    <row r="5728">
+      <c r="A5728" s="2">
+        <v>46087</v>
+      </c>
+      <c r="B5728">
+        <v>819</v>
+      </c>
+      <c r="C5728">
+        <v>0</v>
+      </c>
+      <c r="D5728">
+        <v>0</v>
+      </c>
+      <c r="E5728">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5729">
+      <c r="A5729" s="2">
+        <v>46087</v>
+      </c>
+      <c r="B5729">
+        <v>819</v>
+      </c>
+      <c r="C5729">
+        <v>0</v>
+      </c>
+      <c r="D5729">
+        <v>0</v>
+      </c>
+      <c r="E5729">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="5730">
+      <c r="A5730" s="2">
+        <v>46087</v>
+      </c>
+      <c r="B5730">
+        <v>819</v>
+      </c>
+      <c r="C5730">
+        <v>0</v>
+      </c>
+      <c r="D5730">
+        <v>0</v>
+      </c>
+      <c r="E5730">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5731">
+      <c r="A5731" s="2">
+        <v>46087</v>
+      </c>
+      <c r="B5731">
+        <v>819</v>
+      </c>
+      <c r="C5731">
+        <v>0</v>
+      </c>
+      <c r="D5731">
+        <v>0</v>
+      </c>
+      <c r="E5731">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5732">
+      <c r="A5732" s="2">
+        <v>46087</v>
+      </c>
+      <c r="B5732">
+        <v>819</v>
+      </c>
+      <c r="C5732">
+        <v>0</v>
+      </c>
+      <c r="D5732">
+        <v>0</v>
+      </c>
+      <c r="E5732">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5733">
+      <c r="A5733" s="2">
+        <v>46087</v>
+      </c>
+      <c r="B5733">
+        <v>819</v>
+      </c>
+      <c r="C5733">
+        <v>0</v>
+      </c>
+      <c r="D5733">
+        <v>0</v>
+      </c>
+      <c r="E5733">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5734">
+      <c r="A5734" s="2">
+        <v>46087</v>
+      </c>
+      <c r="B5734">
+        <v>819</v>
+      </c>
+      <c r="C5734">
+        <v>0</v>
+      </c>
+      <c r="D5734">
+        <v>0</v>
+      </c>
+      <c r="E5734">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data-raw/resultados_supersete.xlsx
+++ b/data-raw/resultados_supersete.xlsx
@@ -355,7 +355,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E5734"/>
+  <dimension ref="A1:E5741"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" style="2" customWidth="1"/>
@@ -97849,6 +97849,125 @@
         <v>8</v>
       </c>
     </row>
+    <row r="5735">
+      <c r="A5735" s="2">
+        <v>46090</v>
+      </c>
+      <c r="B5735">
+        <v>820</v>
+      </c>
+      <c r="C5735">
+        <v>0</v>
+      </c>
+      <c r="D5735">
+        <v>0</v>
+      </c>
+      <c r="E5735">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5736">
+      <c r="A5736" s="2">
+        <v>46090</v>
+      </c>
+      <c r="B5736">
+        <v>820</v>
+      </c>
+      <c r="C5736">
+        <v>0</v>
+      </c>
+      <c r="D5736">
+        <v>0</v>
+      </c>
+      <c r="E5736">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5737">
+      <c r="A5737" s="2">
+        <v>46090</v>
+      </c>
+      <c r="B5737">
+        <v>820</v>
+      </c>
+      <c r="C5737">
+        <v>0</v>
+      </c>
+      <c r="D5737">
+        <v>0</v>
+      </c>
+      <c r="E5737">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5738">
+      <c r="A5738" s="2">
+        <v>46090</v>
+      </c>
+      <c r="B5738">
+        <v>820</v>
+      </c>
+      <c r="C5738">
+        <v>0</v>
+      </c>
+      <c r="D5738">
+        <v>0</v>
+      </c>
+      <c r="E5738">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5739">
+      <c r="A5739" s="2">
+        <v>46090</v>
+      </c>
+      <c r="B5739">
+        <v>820</v>
+      </c>
+      <c r="C5739">
+        <v>0</v>
+      </c>
+      <c r="D5739">
+        <v>0</v>
+      </c>
+      <c r="E5739">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5740">
+      <c r="A5740" s="2">
+        <v>46090</v>
+      </c>
+      <c r="B5740">
+        <v>820</v>
+      </c>
+      <c r="C5740">
+        <v>0</v>
+      </c>
+      <c r="D5740">
+        <v>0</v>
+      </c>
+      <c r="E5740">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5741">
+      <c r="A5741" s="2">
+        <v>46090</v>
+      </c>
+      <c r="B5741">
+        <v>820</v>
+      </c>
+      <c r="C5741">
+        <v>0</v>
+      </c>
+      <c r="D5741">
+        <v>0</v>
+      </c>
+      <c r="E5741">
+        <v>5</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data-raw/resultados_supersete.xlsx
+++ b/data-raw/resultados_supersete.xlsx
@@ -355,7 +355,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E5741"/>
+  <dimension ref="A1:E5748"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" style="2" customWidth="1"/>
@@ -97968,6 +97968,125 @@
         <v>5</v>
       </c>
     </row>
+    <row r="5742">
+      <c r="A5742" s="2">
+        <v>46092</v>
+      </c>
+      <c r="B5742">
+        <v>821</v>
+      </c>
+      <c r="C5742">
+        <v>0</v>
+      </c>
+      <c r="D5742">
+        <v>0</v>
+      </c>
+      <c r="E5742">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5743">
+      <c r="A5743" s="2">
+        <v>46092</v>
+      </c>
+      <c r="B5743">
+        <v>821</v>
+      </c>
+      <c r="C5743">
+        <v>0</v>
+      </c>
+      <c r="D5743">
+        <v>0</v>
+      </c>
+      <c r="E5743">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5744">
+      <c r="A5744" s="2">
+        <v>46092</v>
+      </c>
+      <c r="B5744">
+        <v>821</v>
+      </c>
+      <c r="C5744">
+        <v>0</v>
+      </c>
+      <c r="D5744">
+        <v>0</v>
+      </c>
+      <c r="E5744">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5745">
+      <c r="A5745" s="2">
+        <v>46092</v>
+      </c>
+      <c r="B5745">
+        <v>821</v>
+      </c>
+      <c r="C5745">
+        <v>0</v>
+      </c>
+      <c r="D5745">
+        <v>0</v>
+      </c>
+      <c r="E5745">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5746">
+      <c r="A5746" s="2">
+        <v>46092</v>
+      </c>
+      <c r="B5746">
+        <v>821</v>
+      </c>
+      <c r="C5746">
+        <v>0</v>
+      </c>
+      <c r="D5746">
+        <v>0</v>
+      </c>
+      <c r="E5746">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5747">
+      <c r="A5747" s="2">
+        <v>46092</v>
+      </c>
+      <c r="B5747">
+        <v>821</v>
+      </c>
+      <c r="C5747">
+        <v>0</v>
+      </c>
+      <c r="D5747">
+        <v>0</v>
+      </c>
+      <c r="E5747">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5748">
+      <c r="A5748" s="2">
+        <v>46092</v>
+      </c>
+      <c r="B5748">
+        <v>821</v>
+      </c>
+      <c r="C5748">
+        <v>0</v>
+      </c>
+      <c r="D5748">
+        <v>0</v>
+      </c>
+      <c r="E5748">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data-raw/resultados_supersete.xlsx
+++ b/data-raw/resultados_supersete.xlsx
@@ -355,7 +355,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E5748"/>
+  <dimension ref="A1:E5755"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" style="2" customWidth="1"/>
@@ -98087,6 +98087,125 @@
         <v>8</v>
       </c>
     </row>
+    <row r="5749">
+      <c r="A5749" s="2">
+        <v>46094</v>
+      </c>
+      <c r="B5749">
+        <v>822</v>
+      </c>
+      <c r="C5749">
+        <v>0</v>
+      </c>
+      <c r="D5749">
+        <v>0</v>
+      </c>
+      <c r="E5749">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5750">
+      <c r="A5750" s="2">
+        <v>46094</v>
+      </c>
+      <c r="B5750">
+        <v>822</v>
+      </c>
+      <c r="C5750">
+        <v>0</v>
+      </c>
+      <c r="D5750">
+        <v>0</v>
+      </c>
+      <c r="E5750">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5751">
+      <c r="A5751" s="2">
+        <v>46094</v>
+      </c>
+      <c r="B5751">
+        <v>822</v>
+      </c>
+      <c r="C5751">
+        <v>0</v>
+      </c>
+      <c r="D5751">
+        <v>0</v>
+      </c>
+      <c r="E5751">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5752">
+      <c r="A5752" s="2">
+        <v>46094</v>
+      </c>
+      <c r="B5752">
+        <v>822</v>
+      </c>
+      <c r="C5752">
+        <v>0</v>
+      </c>
+      <c r="D5752">
+        <v>0</v>
+      </c>
+      <c r="E5752">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="5753">
+      <c r="A5753" s="2">
+        <v>46094</v>
+      </c>
+      <c r="B5753">
+        <v>822</v>
+      </c>
+      <c r="C5753">
+        <v>0</v>
+      </c>
+      <c r="D5753">
+        <v>0</v>
+      </c>
+      <c r="E5753">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="5754">
+      <c r="A5754" s="2">
+        <v>46094</v>
+      </c>
+      <c r="B5754">
+        <v>822</v>
+      </c>
+      <c r="C5754">
+        <v>0</v>
+      </c>
+      <c r="D5754">
+        <v>0</v>
+      </c>
+      <c r="E5754">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="5755">
+      <c r="A5755" s="2">
+        <v>46094</v>
+      </c>
+      <c r="B5755">
+        <v>822</v>
+      </c>
+      <c r="C5755">
+        <v>0</v>
+      </c>
+      <c r="D5755">
+        <v>0</v>
+      </c>
+      <c r="E5755">
+        <v>4</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data-raw/resultados_supersete.xlsx
+++ b/data-raw/resultados_supersete.xlsx
@@ -355,7 +355,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E5755"/>
+  <dimension ref="A1:E5769"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" style="2" customWidth="1"/>
@@ -98206,6 +98206,244 @@
         <v>4</v>
       </c>
     </row>
+    <row r="5756">
+      <c r="A5756" s="2">
+        <v>46097</v>
+      </c>
+      <c r="B5756">
+        <v>823</v>
+      </c>
+      <c r="C5756">
+        <v>0</v>
+      </c>
+      <c r="D5756">
+        <v>0</v>
+      </c>
+      <c r="E5756">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5757">
+      <c r="A5757" s="2">
+        <v>46097</v>
+      </c>
+      <c r="B5757">
+        <v>823</v>
+      </c>
+      <c r="C5757">
+        <v>0</v>
+      </c>
+      <c r="D5757">
+        <v>0</v>
+      </c>
+      <c r="E5757">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5758">
+      <c r="A5758" s="2">
+        <v>46097</v>
+      </c>
+      <c r="B5758">
+        <v>823</v>
+      </c>
+      <c r="C5758">
+        <v>0</v>
+      </c>
+      <c r="D5758">
+        <v>0</v>
+      </c>
+      <c r="E5758">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5759">
+      <c r="A5759" s="2">
+        <v>46097</v>
+      </c>
+      <c r="B5759">
+        <v>823</v>
+      </c>
+      <c r="C5759">
+        <v>0</v>
+      </c>
+      <c r="D5759">
+        <v>0</v>
+      </c>
+      <c r="E5759">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5760">
+      <c r="A5760" s="2">
+        <v>46097</v>
+      </c>
+      <c r="B5760">
+        <v>823</v>
+      </c>
+      <c r="C5760">
+        <v>0</v>
+      </c>
+      <c r="D5760">
+        <v>0</v>
+      </c>
+      <c r="E5760">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5761">
+      <c r="A5761" s="2">
+        <v>46097</v>
+      </c>
+      <c r="B5761">
+        <v>823</v>
+      </c>
+      <c r="C5761">
+        <v>0</v>
+      </c>
+      <c r="D5761">
+        <v>0</v>
+      </c>
+      <c r="E5761">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5762">
+      <c r="A5762" s="2">
+        <v>46097</v>
+      </c>
+      <c r="B5762">
+        <v>823</v>
+      </c>
+      <c r="C5762">
+        <v>0</v>
+      </c>
+      <c r="D5762">
+        <v>0</v>
+      </c>
+      <c r="E5762">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5763">
+      <c r="A5763" s="2">
+        <v>46099</v>
+      </c>
+      <c r="B5763">
+        <v>824</v>
+      </c>
+      <c r="C5763">
+        <v>0</v>
+      </c>
+      <c r="D5763">
+        <v>0</v>
+      </c>
+      <c r="E5763">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5764">
+      <c r="A5764" s="2">
+        <v>46099</v>
+      </c>
+      <c r="B5764">
+        <v>824</v>
+      </c>
+      <c r="C5764">
+        <v>0</v>
+      </c>
+      <c r="D5764">
+        <v>0</v>
+      </c>
+      <c r="E5764">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5765">
+      <c r="A5765" s="2">
+        <v>46099</v>
+      </c>
+      <c r="B5765">
+        <v>824</v>
+      </c>
+      <c r="C5765">
+        <v>0</v>
+      </c>
+      <c r="D5765">
+        <v>0</v>
+      </c>
+      <c r="E5765">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5766">
+      <c r="A5766" s="2">
+        <v>46099</v>
+      </c>
+      <c r="B5766">
+        <v>824</v>
+      </c>
+      <c r="C5766">
+        <v>0</v>
+      </c>
+      <c r="D5766">
+        <v>0</v>
+      </c>
+      <c r="E5766">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5767">
+      <c r="A5767" s="2">
+        <v>46099</v>
+      </c>
+      <c r="B5767">
+        <v>824</v>
+      </c>
+      <c r="C5767">
+        <v>0</v>
+      </c>
+      <c r="D5767">
+        <v>0</v>
+      </c>
+      <c r="E5767">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5768">
+      <c r="A5768" s="2">
+        <v>46099</v>
+      </c>
+      <c r="B5768">
+        <v>824</v>
+      </c>
+      <c r="C5768">
+        <v>0</v>
+      </c>
+      <c r="D5768">
+        <v>0</v>
+      </c>
+      <c r="E5768">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5769">
+      <c r="A5769" s="2">
+        <v>46099</v>
+      </c>
+      <c r="B5769">
+        <v>824</v>
+      </c>
+      <c r="C5769">
+        <v>0</v>
+      </c>
+      <c r="D5769">
+        <v>0</v>
+      </c>
+      <c r="E5769">
+        <v>5</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data-raw/resultados_supersete.xlsx
+++ b/data-raw/resultados_supersete.xlsx
@@ -355,7 +355,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E5769"/>
+  <dimension ref="A1:E5776"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" style="2" customWidth="1"/>
@@ -98444,6 +98444,125 @@
         <v>5</v>
       </c>
     </row>
+    <row r="5770">
+      <c r="A5770" s="2">
+        <v>46101</v>
+      </c>
+      <c r="B5770">
+        <v>825</v>
+      </c>
+      <c r="C5770">
+        <v>0</v>
+      </c>
+      <c r="D5770">
+        <v>0</v>
+      </c>
+      <c r="E5770">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5771">
+      <c r="A5771" s="2">
+        <v>46101</v>
+      </c>
+      <c r="B5771">
+        <v>825</v>
+      </c>
+      <c r="C5771">
+        <v>0</v>
+      </c>
+      <c r="D5771">
+        <v>0</v>
+      </c>
+      <c r="E5771">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5772">
+      <c r="A5772" s="2">
+        <v>46101</v>
+      </c>
+      <c r="B5772">
+        <v>825</v>
+      </c>
+      <c r="C5772">
+        <v>0</v>
+      </c>
+      <c r="D5772">
+        <v>0</v>
+      </c>
+      <c r="E5772">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5773">
+      <c r="A5773" s="2">
+        <v>46101</v>
+      </c>
+      <c r="B5773">
+        <v>825</v>
+      </c>
+      <c r="C5773">
+        <v>0</v>
+      </c>
+      <c r="D5773">
+        <v>0</v>
+      </c>
+      <c r="E5773">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5774">
+      <c r="A5774" s="2">
+        <v>46101</v>
+      </c>
+      <c r="B5774">
+        <v>825</v>
+      </c>
+      <c r="C5774">
+        <v>0</v>
+      </c>
+      <c r="D5774">
+        <v>0</v>
+      </c>
+      <c r="E5774">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5775">
+      <c r="A5775" s="2">
+        <v>46101</v>
+      </c>
+      <c r="B5775">
+        <v>825</v>
+      </c>
+      <c r="C5775">
+        <v>0</v>
+      </c>
+      <c r="D5775">
+        <v>0</v>
+      </c>
+      <c r="E5775">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5776">
+      <c r="A5776" s="2">
+        <v>46101</v>
+      </c>
+      <c r="B5776">
+        <v>825</v>
+      </c>
+      <c r="C5776">
+        <v>0</v>
+      </c>
+      <c r="D5776">
+        <v>0</v>
+      </c>
+      <c r="E5776">
+        <v>3</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data-raw/resultados_supersete.xlsx
+++ b/data-raw/resultados_supersete.xlsx
@@ -355,7 +355,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E5776"/>
+  <dimension ref="A1:E5783"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" style="2" customWidth="1"/>
@@ -98563,6 +98563,125 @@
         <v>3</v>
       </c>
     </row>
+    <row r="5777">
+      <c r="A5777" s="2">
+        <v>46104</v>
+      </c>
+      <c r="B5777">
+        <v>826</v>
+      </c>
+      <c r="C5777">
+        <v>0</v>
+      </c>
+      <c r="D5777">
+        <v>0</v>
+      </c>
+      <c r="E5777">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5778">
+      <c r="A5778" s="2">
+        <v>46104</v>
+      </c>
+      <c r="B5778">
+        <v>826</v>
+      </c>
+      <c r="C5778">
+        <v>0</v>
+      </c>
+      <c r="D5778">
+        <v>0</v>
+      </c>
+      <c r="E5778">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5779">
+      <c r="A5779" s="2">
+        <v>46104</v>
+      </c>
+      <c r="B5779">
+        <v>826</v>
+      </c>
+      <c r="C5779">
+        <v>0</v>
+      </c>
+      <c r="D5779">
+        <v>0</v>
+      </c>
+      <c r="E5779">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="5780">
+      <c r="A5780" s="2">
+        <v>46104</v>
+      </c>
+      <c r="B5780">
+        <v>826</v>
+      </c>
+      <c r="C5780">
+        <v>0</v>
+      </c>
+      <c r="D5780">
+        <v>0</v>
+      </c>
+      <c r="E5780">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5781">
+      <c r="A5781" s="2">
+        <v>46104</v>
+      </c>
+      <c r="B5781">
+        <v>826</v>
+      </c>
+      <c r="C5781">
+        <v>0</v>
+      </c>
+      <c r="D5781">
+        <v>0</v>
+      </c>
+      <c r="E5781">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5782">
+      <c r="A5782" s="2">
+        <v>46104</v>
+      </c>
+      <c r="B5782">
+        <v>826</v>
+      </c>
+      <c r="C5782">
+        <v>0</v>
+      </c>
+      <c r="D5782">
+        <v>0</v>
+      </c>
+      <c r="E5782">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5783">
+      <c r="A5783" s="2">
+        <v>46104</v>
+      </c>
+      <c r="B5783">
+        <v>826</v>
+      </c>
+      <c r="C5783">
+        <v>0</v>
+      </c>
+      <c r="D5783">
+        <v>0</v>
+      </c>
+      <c r="E5783">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data-raw/resultados_supersete.xlsx
+++ b/data-raw/resultados_supersete.xlsx
@@ -355,7 +355,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E5783"/>
+  <dimension ref="A1:E5790"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" style="2" customWidth="1"/>
@@ -98682,6 +98682,125 @@
         <v>0</v>
       </c>
     </row>
+    <row r="5784">
+      <c r="A5784" s="2">
+        <v>46106</v>
+      </c>
+      <c r="B5784">
+        <v>827</v>
+      </c>
+      <c r="C5784">
+        <v>0</v>
+      </c>
+      <c r="D5784">
+        <v>0</v>
+      </c>
+      <c r="E5784">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5785">
+      <c r="A5785" s="2">
+        <v>46106</v>
+      </c>
+      <c r="B5785">
+        <v>827</v>
+      </c>
+      <c r="C5785">
+        <v>0</v>
+      </c>
+      <c r="D5785">
+        <v>0</v>
+      </c>
+      <c r="E5785">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5786">
+      <c r="A5786" s="2">
+        <v>46106</v>
+      </c>
+      <c r="B5786">
+        <v>827</v>
+      </c>
+      <c r="C5786">
+        <v>0</v>
+      </c>
+      <c r="D5786">
+        <v>0</v>
+      </c>
+      <c r="E5786">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5787">
+      <c r="A5787" s="2">
+        <v>46106</v>
+      </c>
+      <c r="B5787">
+        <v>827</v>
+      </c>
+      <c r="C5787">
+        <v>0</v>
+      </c>
+      <c r="D5787">
+        <v>0</v>
+      </c>
+      <c r="E5787">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5788">
+      <c r="A5788" s="2">
+        <v>46106</v>
+      </c>
+      <c r="B5788">
+        <v>827</v>
+      </c>
+      <c r="C5788">
+        <v>0</v>
+      </c>
+      <c r="D5788">
+        <v>0</v>
+      </c>
+      <c r="E5788">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5789">
+      <c r="A5789" s="2">
+        <v>46106</v>
+      </c>
+      <c r="B5789">
+        <v>827</v>
+      </c>
+      <c r="C5789">
+        <v>0</v>
+      </c>
+      <c r="D5789">
+        <v>0</v>
+      </c>
+      <c r="E5789">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5790">
+      <c r="A5790" s="2">
+        <v>46106</v>
+      </c>
+      <c r="B5790">
+        <v>827</v>
+      </c>
+      <c r="C5790">
+        <v>0</v>
+      </c>
+      <c r="D5790">
+        <v>0</v>
+      </c>
+      <c r="E5790">
+        <v>3</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data-raw/resultados_supersete.xlsx
+++ b/data-raw/resultados_supersete.xlsx
@@ -355,7 +355,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E5790"/>
+  <dimension ref="A1:E5797"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" style="2" customWidth="1"/>
@@ -98801,6 +98801,125 @@
         <v>3</v>
       </c>
     </row>
+    <row r="5791">
+      <c r="A5791" s="2">
+        <v>46108</v>
+      </c>
+      <c r="B5791">
+        <v>828</v>
+      </c>
+      <c r="C5791">
+        <v>0</v>
+      </c>
+      <c r="D5791">
+        <v>0</v>
+      </c>
+      <c r="E5791">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5792">
+      <c r="A5792" s="2">
+        <v>46108</v>
+      </c>
+      <c r="B5792">
+        <v>828</v>
+      </c>
+      <c r="C5792">
+        <v>0</v>
+      </c>
+      <c r="D5792">
+        <v>0</v>
+      </c>
+      <c r="E5792">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5793">
+      <c r="A5793" s="2">
+        <v>46108</v>
+      </c>
+      <c r="B5793">
+        <v>828</v>
+      </c>
+      <c r="C5793">
+        <v>0</v>
+      </c>
+      <c r="D5793">
+        <v>0</v>
+      </c>
+      <c r="E5793">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5794">
+      <c r="A5794" s="2">
+        <v>46108</v>
+      </c>
+      <c r="B5794">
+        <v>828</v>
+      </c>
+      <c r="C5794">
+        <v>0</v>
+      </c>
+      <c r="D5794">
+        <v>0</v>
+      </c>
+      <c r="E5794">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5795">
+      <c r="A5795" s="2">
+        <v>46108</v>
+      </c>
+      <c r="B5795">
+        <v>828</v>
+      </c>
+      <c r="C5795">
+        <v>0</v>
+      </c>
+      <c r="D5795">
+        <v>0</v>
+      </c>
+      <c r="E5795">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5796">
+      <c r="A5796" s="2">
+        <v>46108</v>
+      </c>
+      <c r="B5796">
+        <v>828</v>
+      </c>
+      <c r="C5796">
+        <v>0</v>
+      </c>
+      <c r="D5796">
+        <v>0</v>
+      </c>
+      <c r="E5796">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5797">
+      <c r="A5797" s="2">
+        <v>46108</v>
+      </c>
+      <c r="B5797">
+        <v>828</v>
+      </c>
+      <c r="C5797">
+        <v>0</v>
+      </c>
+      <c r="D5797">
+        <v>0</v>
+      </c>
+      <c r="E5797">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data-raw/resultados_supersete.xlsx
+++ b/data-raw/resultados_supersete.xlsx
@@ -355,7 +355,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E5797"/>
+  <dimension ref="A1:E5804"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" style="2" customWidth="1"/>
@@ -98920,6 +98920,125 @@
         <v>9</v>
       </c>
     </row>
+    <row r="5798">
+      <c r="A5798" s="2">
+        <v>46111</v>
+      </c>
+      <c r="B5798">
+        <v>829</v>
+      </c>
+      <c r="C5798">
+        <v>0</v>
+      </c>
+      <c r="D5798">
+        <v>0</v>
+      </c>
+      <c r="E5798">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5799">
+      <c r="A5799" s="2">
+        <v>46111</v>
+      </c>
+      <c r="B5799">
+        <v>829</v>
+      </c>
+      <c r="C5799">
+        <v>0</v>
+      </c>
+      <c r="D5799">
+        <v>0</v>
+      </c>
+      <c r="E5799">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5800">
+      <c r="A5800" s="2">
+        <v>46111</v>
+      </c>
+      <c r="B5800">
+        <v>829</v>
+      </c>
+      <c r="C5800">
+        <v>0</v>
+      </c>
+      <c r="D5800">
+        <v>0</v>
+      </c>
+      <c r="E5800">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5801">
+      <c r="A5801" s="2">
+        <v>46111</v>
+      </c>
+      <c r="B5801">
+        <v>829</v>
+      </c>
+      <c r="C5801">
+        <v>0</v>
+      </c>
+      <c r="D5801">
+        <v>0</v>
+      </c>
+      <c r="E5801">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5802">
+      <c r="A5802" s="2">
+        <v>46111</v>
+      </c>
+      <c r="B5802">
+        <v>829</v>
+      </c>
+      <c r="C5802">
+        <v>0</v>
+      </c>
+      <c r="D5802">
+        <v>0</v>
+      </c>
+      <c r="E5802">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5803">
+      <c r="A5803" s="2">
+        <v>46111</v>
+      </c>
+      <c r="B5803">
+        <v>829</v>
+      </c>
+      <c r="C5803">
+        <v>0</v>
+      </c>
+      <c r="D5803">
+        <v>0</v>
+      </c>
+      <c r="E5803">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5804">
+      <c r="A5804" s="2">
+        <v>46111</v>
+      </c>
+      <c r="B5804">
+        <v>829</v>
+      </c>
+      <c r="C5804">
+        <v>0</v>
+      </c>
+      <c r="D5804">
+        <v>0</v>
+      </c>
+      <c r="E5804">
+        <v>5</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data-raw/resultados_supersete.xlsx
+++ b/data-raw/resultados_supersete.xlsx
@@ -355,7 +355,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E5804"/>
+  <dimension ref="A1:E5811"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" style="2" customWidth="1"/>
@@ -99039,6 +99039,125 @@
         <v>5</v>
       </c>
     </row>
+    <row r="5805">
+      <c r="A5805" s="2">
+        <v>46113</v>
+      </c>
+      <c r="B5805">
+        <v>830</v>
+      </c>
+      <c r="C5805">
+        <v>0</v>
+      </c>
+      <c r="D5805">
+        <v>0</v>
+      </c>
+      <c r="E5805">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5806">
+      <c r="A5806" s="2">
+        <v>46113</v>
+      </c>
+      <c r="B5806">
+        <v>830</v>
+      </c>
+      <c r="C5806">
+        <v>0</v>
+      </c>
+      <c r="D5806">
+        <v>0</v>
+      </c>
+      <c r="E5806">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5807">
+      <c r="A5807" s="2">
+        <v>46113</v>
+      </c>
+      <c r="B5807">
+        <v>830</v>
+      </c>
+      <c r="C5807">
+        <v>0</v>
+      </c>
+      <c r="D5807">
+        <v>0</v>
+      </c>
+      <c r="E5807">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5808">
+      <c r="A5808" s="2">
+        <v>46113</v>
+      </c>
+      <c r="B5808">
+        <v>830</v>
+      </c>
+      <c r="C5808">
+        <v>0</v>
+      </c>
+      <c r="D5808">
+        <v>0</v>
+      </c>
+      <c r="E5808">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5809">
+      <c r="A5809" s="2">
+        <v>46113</v>
+      </c>
+      <c r="B5809">
+        <v>830</v>
+      </c>
+      <c r="C5809">
+        <v>0</v>
+      </c>
+      <c r="D5809">
+        <v>0</v>
+      </c>
+      <c r="E5809">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5810">
+      <c r="A5810" s="2">
+        <v>46113</v>
+      </c>
+      <c r="B5810">
+        <v>830</v>
+      </c>
+      <c r="C5810">
+        <v>0</v>
+      </c>
+      <c r="D5810">
+        <v>0</v>
+      </c>
+      <c r="E5810">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5811">
+      <c r="A5811" s="2">
+        <v>46113</v>
+      </c>
+      <c r="B5811">
+        <v>830</v>
+      </c>
+      <c r="C5811">
+        <v>0</v>
+      </c>
+      <c r="D5811">
+        <v>0</v>
+      </c>
+      <c r="E5811">
+        <v>4</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data-raw/resultados_supersete.xlsx
+++ b/data-raw/resultados_supersete.xlsx
@@ -355,7 +355,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E5811"/>
+  <dimension ref="A1:E5818"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" style="2" customWidth="1"/>
@@ -99158,6 +99158,125 @@
         <v>4</v>
       </c>
     </row>
+    <row r="5812">
+      <c r="A5812" s="2">
+        <v>46118</v>
+      </c>
+      <c r="B5812">
+        <v>831</v>
+      </c>
+      <c r="C5812">
+        <v>0</v>
+      </c>
+      <c r="D5812">
+        <v>0</v>
+      </c>
+      <c r="E5812">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5813">
+      <c r="A5813" s="2">
+        <v>46118</v>
+      </c>
+      <c r="B5813">
+        <v>831</v>
+      </c>
+      <c r="C5813">
+        <v>0</v>
+      </c>
+      <c r="D5813">
+        <v>0</v>
+      </c>
+      <c r="E5813">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5814">
+      <c r="A5814" s="2">
+        <v>46118</v>
+      </c>
+      <c r="B5814">
+        <v>831</v>
+      </c>
+      <c r="C5814">
+        <v>0</v>
+      </c>
+      <c r="D5814">
+        <v>0</v>
+      </c>
+      <c r="E5814">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5815">
+      <c r="A5815" s="2">
+        <v>46118</v>
+      </c>
+      <c r="B5815">
+        <v>831</v>
+      </c>
+      <c r="C5815">
+        <v>0</v>
+      </c>
+      <c r="D5815">
+        <v>0</v>
+      </c>
+      <c r="E5815">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5816">
+      <c r="A5816" s="2">
+        <v>46118</v>
+      </c>
+      <c r="B5816">
+        <v>831</v>
+      </c>
+      <c r="C5816">
+        <v>0</v>
+      </c>
+      <c r="D5816">
+        <v>0</v>
+      </c>
+      <c r="E5816">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5817">
+      <c r="A5817" s="2">
+        <v>46118</v>
+      </c>
+      <c r="B5817">
+        <v>831</v>
+      </c>
+      <c r="C5817">
+        <v>0</v>
+      </c>
+      <c r="D5817">
+        <v>0</v>
+      </c>
+      <c r="E5817">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5818">
+      <c r="A5818" s="2">
+        <v>46118</v>
+      </c>
+      <c r="B5818">
+        <v>831</v>
+      </c>
+      <c r="C5818">
+        <v>0</v>
+      </c>
+      <c r="D5818">
+        <v>0</v>
+      </c>
+      <c r="E5818">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data-raw/resultados_supersete.xlsx
+++ b/data-raw/resultados_supersete.xlsx
@@ -355,7 +355,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E5818"/>
+  <dimension ref="A1:E5825"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" style="2" customWidth="1"/>
@@ -99277,6 +99277,125 @@
         <v>8</v>
       </c>
     </row>
+    <row r="5819">
+      <c r="A5819" s="2">
+        <v>46120</v>
+      </c>
+      <c r="B5819">
+        <v>832</v>
+      </c>
+      <c r="C5819">
+        <v>0</v>
+      </c>
+      <c r="D5819">
+        <v>0</v>
+      </c>
+      <c r="E5819">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5820">
+      <c r="A5820" s="2">
+        <v>46120</v>
+      </c>
+      <c r="B5820">
+        <v>832</v>
+      </c>
+      <c r="C5820">
+        <v>0</v>
+      </c>
+      <c r="D5820">
+        <v>0</v>
+      </c>
+      <c r="E5820">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5821">
+      <c r="A5821" s="2">
+        <v>46120</v>
+      </c>
+      <c r="B5821">
+        <v>832</v>
+      </c>
+      <c r="C5821">
+        <v>0</v>
+      </c>
+      <c r="D5821">
+        <v>0</v>
+      </c>
+      <c r="E5821">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5822">
+      <c r="A5822" s="2">
+        <v>46120</v>
+      </c>
+      <c r="B5822">
+        <v>832</v>
+      </c>
+      <c r="C5822">
+        <v>0</v>
+      </c>
+      <c r="D5822">
+        <v>0</v>
+      </c>
+      <c r="E5822">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5823">
+      <c r="A5823" s="2">
+        <v>46120</v>
+      </c>
+      <c r="B5823">
+        <v>832</v>
+      </c>
+      <c r="C5823">
+        <v>0</v>
+      </c>
+      <c r="D5823">
+        <v>0</v>
+      </c>
+      <c r="E5823">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5824">
+      <c r="A5824" s="2">
+        <v>46120</v>
+      </c>
+      <c r="B5824">
+        <v>832</v>
+      </c>
+      <c r="C5824">
+        <v>0</v>
+      </c>
+      <c r="D5824">
+        <v>0</v>
+      </c>
+      <c r="E5824">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5825">
+      <c r="A5825" s="2">
+        <v>46120</v>
+      </c>
+      <c r="B5825">
+        <v>832</v>
+      </c>
+      <c r="C5825">
+        <v>0</v>
+      </c>
+      <c r="D5825">
+        <v>0</v>
+      </c>
+      <c r="E5825">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data-raw/resultados_supersete.xlsx
+++ b/data-raw/resultados_supersete.xlsx
@@ -355,7 +355,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E5825"/>
+  <dimension ref="A1:E5832"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" style="2" customWidth="1"/>
@@ -99396,6 +99396,125 @@
         <v>8</v>
       </c>
     </row>
+    <row r="5826">
+      <c r="A5826" s="2">
+        <v>46122</v>
+      </c>
+      <c r="B5826">
+        <v>833</v>
+      </c>
+      <c r="C5826">
+        <v>0</v>
+      </c>
+      <c r="D5826">
+        <v>0</v>
+      </c>
+      <c r="E5826">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5827">
+      <c r="A5827" s="2">
+        <v>46122</v>
+      </c>
+      <c r="B5827">
+        <v>833</v>
+      </c>
+      <c r="C5827">
+        <v>0</v>
+      </c>
+      <c r="D5827">
+        <v>0</v>
+      </c>
+      <c r="E5827">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="5828">
+      <c r="A5828" s="2">
+        <v>46122</v>
+      </c>
+      <c r="B5828">
+        <v>833</v>
+      </c>
+      <c r="C5828">
+        <v>0</v>
+      </c>
+      <c r="D5828">
+        <v>0</v>
+      </c>
+      <c r="E5828">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5829">
+      <c r="A5829" s="2">
+        <v>46122</v>
+      </c>
+      <c r="B5829">
+        <v>833</v>
+      </c>
+      <c r="C5829">
+        <v>0</v>
+      </c>
+      <c r="D5829">
+        <v>0</v>
+      </c>
+      <c r="E5829">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="5830">
+      <c r="A5830" s="2">
+        <v>46122</v>
+      </c>
+      <c r="B5830">
+        <v>833</v>
+      </c>
+      <c r="C5830">
+        <v>0</v>
+      </c>
+      <c r="D5830">
+        <v>0</v>
+      </c>
+      <c r="E5830">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5831">
+      <c r="A5831" s="2">
+        <v>46122</v>
+      </c>
+      <c r="B5831">
+        <v>833</v>
+      </c>
+      <c r="C5831">
+        <v>0</v>
+      </c>
+      <c r="D5831">
+        <v>0</v>
+      </c>
+      <c r="E5831">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5832">
+      <c r="A5832" s="2">
+        <v>46122</v>
+      </c>
+      <c r="B5832">
+        <v>833</v>
+      </c>
+      <c r="C5832">
+        <v>0</v>
+      </c>
+      <c r="D5832">
+        <v>0</v>
+      </c>
+      <c r="E5832">
+        <v>2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data-raw/resultados_supersete.xlsx
+++ b/data-raw/resultados_supersete.xlsx
@@ -355,7 +355,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E5832"/>
+  <dimension ref="A1:E5839"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" style="2" customWidth="1"/>
@@ -99515,6 +99515,125 @@
         <v>2</v>
       </c>
     </row>
+    <row r="5833">
+      <c r="A5833" s="2">
+        <v>46125</v>
+      </c>
+      <c r="B5833">
+        <v>834</v>
+      </c>
+      <c r="C5833">
+        <v>0</v>
+      </c>
+      <c r="D5833">
+        <v>0</v>
+      </c>
+      <c r="E5833">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5834">
+      <c r="A5834" s="2">
+        <v>46125</v>
+      </c>
+      <c r="B5834">
+        <v>834</v>
+      </c>
+      <c r="C5834">
+        <v>0</v>
+      </c>
+      <c r="D5834">
+        <v>0</v>
+      </c>
+      <c r="E5834">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5835">
+      <c r="A5835" s="2">
+        <v>46125</v>
+      </c>
+      <c r="B5835">
+        <v>834</v>
+      </c>
+      <c r="C5835">
+        <v>0</v>
+      </c>
+      <c r="D5835">
+        <v>0</v>
+      </c>
+      <c r="E5835">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5836">
+      <c r="A5836" s="2">
+        <v>46125</v>
+      </c>
+      <c r="B5836">
+        <v>834</v>
+      </c>
+      <c r="C5836">
+        <v>0</v>
+      </c>
+      <c r="D5836">
+        <v>0</v>
+      </c>
+      <c r="E5836">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5837">
+      <c r="A5837" s="2">
+        <v>46125</v>
+      </c>
+      <c r="B5837">
+        <v>834</v>
+      </c>
+      <c r="C5837">
+        <v>0</v>
+      </c>
+      <c r="D5837">
+        <v>0</v>
+      </c>
+      <c r="E5837">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5838">
+      <c r="A5838" s="2">
+        <v>46125</v>
+      </c>
+      <c r="B5838">
+        <v>834</v>
+      </c>
+      <c r="C5838">
+        <v>0</v>
+      </c>
+      <c r="D5838">
+        <v>0</v>
+      </c>
+      <c r="E5838">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5839">
+      <c r="A5839" s="2">
+        <v>46125</v>
+      </c>
+      <c r="B5839">
+        <v>834</v>
+      </c>
+      <c r="C5839">
+        <v>0</v>
+      </c>
+      <c r="D5839">
+        <v>0</v>
+      </c>
+      <c r="E5839">
+        <v>4</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data-raw/resultados_supersete.xlsx
+++ b/data-raw/resultados_supersete.xlsx
@@ -355,7 +355,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E5839"/>
+  <dimension ref="A1:E5846"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" style="2" customWidth="1"/>
@@ -99634,6 +99634,125 @@
         <v>4</v>
       </c>
     </row>
+    <row r="5840">
+      <c r="A5840" s="2">
+        <v>46127</v>
+      </c>
+      <c r="B5840">
+        <v>835</v>
+      </c>
+      <c r="C5840">
+        <v>0</v>
+      </c>
+      <c r="D5840">
+        <v>0</v>
+      </c>
+      <c r="E5840">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5841">
+      <c r="A5841" s="2">
+        <v>46127</v>
+      </c>
+      <c r="B5841">
+        <v>835</v>
+      </c>
+      <c r="C5841">
+        <v>0</v>
+      </c>
+      <c r="D5841">
+        <v>0</v>
+      </c>
+      <c r="E5841">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5842">
+      <c r="A5842" s="2">
+        <v>46127</v>
+      </c>
+      <c r="B5842">
+        <v>835</v>
+      </c>
+      <c r="C5842">
+        <v>0</v>
+      </c>
+      <c r="D5842">
+        <v>0</v>
+      </c>
+      <c r="E5842">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5843">
+      <c r="A5843" s="2">
+        <v>46127</v>
+      </c>
+      <c r="B5843">
+        <v>835</v>
+      </c>
+      <c r="C5843">
+        <v>0</v>
+      </c>
+      <c r="D5843">
+        <v>0</v>
+      </c>
+      <c r="E5843">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5844">
+      <c r="A5844" s="2">
+        <v>46127</v>
+      </c>
+      <c r="B5844">
+        <v>835</v>
+      </c>
+      <c r="C5844">
+        <v>0</v>
+      </c>
+      <c r="D5844">
+        <v>0</v>
+      </c>
+      <c r="E5844">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="5845">
+      <c r="A5845" s="2">
+        <v>46127</v>
+      </c>
+      <c r="B5845">
+        <v>835</v>
+      </c>
+      <c r="C5845">
+        <v>0</v>
+      </c>
+      <c r="D5845">
+        <v>0</v>
+      </c>
+      <c r="E5845">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5846">
+      <c r="A5846" s="2">
+        <v>46127</v>
+      </c>
+      <c r="B5846">
+        <v>835</v>
+      </c>
+      <c r="C5846">
+        <v>0</v>
+      </c>
+      <c r="D5846">
+        <v>0</v>
+      </c>
+      <c r="E5846">
+        <v>3</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data-raw/resultados_supersete.xlsx
+++ b/data-raw/resultados_supersete.xlsx
@@ -355,7 +355,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E5846"/>
+  <dimension ref="A1:E5853"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" style="2" customWidth="1"/>
@@ -99753,6 +99753,125 @@
         <v>3</v>
       </c>
     </row>
+    <row r="5847">
+      <c r="A5847" s="2">
+        <v>46129</v>
+      </c>
+      <c r="B5847">
+        <v>836</v>
+      </c>
+      <c r="C5847">
+        <v>0</v>
+      </c>
+      <c r="D5847">
+        <v>0</v>
+      </c>
+      <c r="E5847">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5848">
+      <c r="A5848" s="2">
+        <v>46129</v>
+      </c>
+      <c r="B5848">
+        <v>836</v>
+      </c>
+      <c r="C5848">
+        <v>0</v>
+      </c>
+      <c r="D5848">
+        <v>0</v>
+      </c>
+      <c r="E5848">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5849">
+      <c r="A5849" s="2">
+        <v>46129</v>
+      </c>
+      <c r="B5849">
+        <v>836</v>
+      </c>
+      <c r="C5849">
+        <v>0</v>
+      </c>
+      <c r="D5849">
+        <v>0</v>
+      </c>
+      <c r="E5849">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5850">
+      <c r="A5850" s="2">
+        <v>46129</v>
+      </c>
+      <c r="B5850">
+        <v>836</v>
+      </c>
+      <c r="C5850">
+        <v>0</v>
+      </c>
+      <c r="D5850">
+        <v>0</v>
+      </c>
+      <c r="E5850">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5851">
+      <c r="A5851" s="2">
+        <v>46129</v>
+      </c>
+      <c r="B5851">
+        <v>836</v>
+      </c>
+      <c r="C5851">
+        <v>0</v>
+      </c>
+      <c r="D5851">
+        <v>0</v>
+      </c>
+      <c r="E5851">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5852">
+      <c r="A5852" s="2">
+        <v>46129</v>
+      </c>
+      <c r="B5852">
+        <v>836</v>
+      </c>
+      <c r="C5852">
+        <v>0</v>
+      </c>
+      <c r="D5852">
+        <v>0</v>
+      </c>
+      <c r="E5852">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5853">
+      <c r="A5853" s="2">
+        <v>46129</v>
+      </c>
+      <c r="B5853">
+        <v>836</v>
+      </c>
+      <c r="C5853">
+        <v>0</v>
+      </c>
+      <c r="D5853">
+        <v>0</v>
+      </c>
+      <c r="E5853">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data-raw/resultados_supersete.xlsx
+++ b/data-raw/resultados_supersete.xlsx
@@ -355,7 +355,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E5853"/>
+  <dimension ref="A1:E5860"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" style="2" customWidth="1"/>
@@ -99872,6 +99872,125 @@
         <v>7</v>
       </c>
     </row>
+    <row r="5854">
+      <c r="A5854" s="2">
+        <v>46132</v>
+      </c>
+      <c r="B5854">
+        <v>837</v>
+      </c>
+      <c r="C5854">
+        <v>0</v>
+      </c>
+      <c r="D5854">
+        <v>0</v>
+      </c>
+      <c r="E5854">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5855">
+      <c r="A5855" s="2">
+        <v>46132</v>
+      </c>
+      <c r="B5855">
+        <v>837</v>
+      </c>
+      <c r="C5855">
+        <v>0</v>
+      </c>
+      <c r="D5855">
+        <v>0</v>
+      </c>
+      <c r="E5855">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5856">
+      <c r="A5856" s="2">
+        <v>46132</v>
+      </c>
+      <c r="B5856">
+        <v>837</v>
+      </c>
+      <c r="C5856">
+        <v>0</v>
+      </c>
+      <c r="D5856">
+        <v>0</v>
+      </c>
+      <c r="E5856">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5857">
+      <c r="A5857" s="2">
+        <v>46132</v>
+      </c>
+      <c r="B5857">
+        <v>837</v>
+      </c>
+      <c r="C5857">
+        <v>0</v>
+      </c>
+      <c r="D5857">
+        <v>0</v>
+      </c>
+      <c r="E5857">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5858">
+      <c r="A5858" s="2">
+        <v>46132</v>
+      </c>
+      <c r="B5858">
+        <v>837</v>
+      </c>
+      <c r="C5858">
+        <v>0</v>
+      </c>
+      <c r="D5858">
+        <v>0</v>
+      </c>
+      <c r="E5858">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5859">
+      <c r="A5859" s="2">
+        <v>46132</v>
+      </c>
+      <c r="B5859">
+        <v>837</v>
+      </c>
+      <c r="C5859">
+        <v>0</v>
+      </c>
+      <c r="D5859">
+        <v>0</v>
+      </c>
+      <c r="E5859">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5860">
+      <c r="A5860" s="2">
+        <v>46132</v>
+      </c>
+      <c r="B5860">
+        <v>837</v>
+      </c>
+      <c r="C5860">
+        <v>0</v>
+      </c>
+      <c r="D5860">
+        <v>0</v>
+      </c>
+      <c r="E5860">
+        <v>4</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data-raw/resultados_supersete.xlsx
+++ b/data-raw/resultados_supersete.xlsx
@@ -355,7 +355,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E5860"/>
+  <dimension ref="A1:E5867"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" style="2" customWidth="1"/>
@@ -99991,6 +99991,125 @@
         <v>4</v>
       </c>
     </row>
+    <row r="5861">
+      <c r="A5861" s="2">
+        <v>46134</v>
+      </c>
+      <c r="B5861">
+        <v>838</v>
+      </c>
+      <c r="C5861">
+        <v>0</v>
+      </c>
+      <c r="D5861">
+        <v>0</v>
+      </c>
+      <c r="E5861">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5862">
+      <c r="A5862" s="2">
+        <v>46134</v>
+      </c>
+      <c r="B5862">
+        <v>838</v>
+      </c>
+      <c r="C5862">
+        <v>0</v>
+      </c>
+      <c r="D5862">
+        <v>0</v>
+      </c>
+      <c r="E5862">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5863">
+      <c r="A5863" s="2">
+        <v>46134</v>
+      </c>
+      <c r="B5863">
+        <v>838</v>
+      </c>
+      <c r="C5863">
+        <v>0</v>
+      </c>
+      <c r="D5863">
+        <v>0</v>
+      </c>
+      <c r="E5863">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5864">
+      <c r="A5864" s="2">
+        <v>46134</v>
+      </c>
+      <c r="B5864">
+        <v>838</v>
+      </c>
+      <c r="C5864">
+        <v>0</v>
+      </c>
+      <c r="D5864">
+        <v>0</v>
+      </c>
+      <c r="E5864">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5865">
+      <c r="A5865" s="2">
+        <v>46134</v>
+      </c>
+      <c r="B5865">
+        <v>838</v>
+      </c>
+      <c r="C5865">
+        <v>0</v>
+      </c>
+      <c r="D5865">
+        <v>0</v>
+      </c>
+      <c r="E5865">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5866">
+      <c r="A5866" s="2">
+        <v>46134</v>
+      </c>
+      <c r="B5866">
+        <v>838</v>
+      </c>
+      <c r="C5866">
+        <v>0</v>
+      </c>
+      <c r="D5866">
+        <v>0</v>
+      </c>
+      <c r="E5866">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5867">
+      <c r="A5867" s="2">
+        <v>46134</v>
+      </c>
+      <c r="B5867">
+        <v>838</v>
+      </c>
+      <c r="C5867">
+        <v>0</v>
+      </c>
+      <c r="D5867">
+        <v>0</v>
+      </c>
+      <c r="E5867">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data-raw/resultados_supersete.xlsx
+++ b/data-raw/resultados_supersete.xlsx
@@ -355,7 +355,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E5867"/>
+  <dimension ref="A1:E5874"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" style="2" customWidth="1"/>
@@ -100110,6 +100110,125 @@
         <v>1</v>
       </c>
     </row>
+    <row r="5868">
+      <c r="A5868" s="2">
+        <v>46136</v>
+      </c>
+      <c r="B5868">
+        <v>839</v>
+      </c>
+      <c r="C5868">
+        <v>0</v>
+      </c>
+      <c r="D5868">
+        <v>0</v>
+      </c>
+      <c r="E5868">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5869">
+      <c r="A5869" s="2">
+        <v>46136</v>
+      </c>
+      <c r="B5869">
+        <v>839</v>
+      </c>
+      <c r="C5869">
+        <v>0</v>
+      </c>
+      <c r="D5869">
+        <v>0</v>
+      </c>
+      <c r="E5869">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5870">
+      <c r="A5870" s="2">
+        <v>46136</v>
+      </c>
+      <c r="B5870">
+        <v>839</v>
+      </c>
+      <c r="C5870">
+        <v>0</v>
+      </c>
+      <c r="D5870">
+        <v>0</v>
+      </c>
+      <c r="E5870">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5871">
+      <c r="A5871" s="2">
+        <v>46136</v>
+      </c>
+      <c r="B5871">
+        <v>839</v>
+      </c>
+      <c r="C5871">
+        <v>0</v>
+      </c>
+      <c r="D5871">
+        <v>0</v>
+      </c>
+      <c r="E5871">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5872">
+      <c r="A5872" s="2">
+        <v>46136</v>
+      </c>
+      <c r="B5872">
+        <v>839</v>
+      </c>
+      <c r="C5872">
+        <v>0</v>
+      </c>
+      <c r="D5872">
+        <v>0</v>
+      </c>
+      <c r="E5872">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5873">
+      <c r="A5873" s="2">
+        <v>46136</v>
+      </c>
+      <c r="B5873">
+        <v>839</v>
+      </c>
+      <c r="C5873">
+        <v>0</v>
+      </c>
+      <c r="D5873">
+        <v>0</v>
+      </c>
+      <c r="E5873">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5874">
+      <c r="A5874" s="2">
+        <v>46136</v>
+      </c>
+      <c r="B5874">
+        <v>839</v>
+      </c>
+      <c r="C5874">
+        <v>0</v>
+      </c>
+      <c r="D5874">
+        <v>0</v>
+      </c>
+      <c r="E5874">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data-raw/resultados_supersete.xlsx
+++ b/data-raw/resultados_supersete.xlsx
@@ -355,7 +355,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E5874"/>
+  <dimension ref="A1:E5881"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" style="2" customWidth="1"/>
@@ -100229,6 +100229,125 @@
         <v>7</v>
       </c>
     </row>
+    <row r="5875">
+      <c r="A5875" s="2">
+        <v>46139</v>
+      </c>
+      <c r="B5875">
+        <v>840</v>
+      </c>
+      <c r="C5875">
+        <v>0</v>
+      </c>
+      <c r="D5875">
+        <v>0</v>
+      </c>
+      <c r="E5875">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5876">
+      <c r="A5876" s="2">
+        <v>46139</v>
+      </c>
+      <c r="B5876">
+        <v>840</v>
+      </c>
+      <c r="C5876">
+        <v>0</v>
+      </c>
+      <c r="D5876">
+        <v>0</v>
+      </c>
+      <c r="E5876">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5877">
+      <c r="A5877" s="2">
+        <v>46139</v>
+      </c>
+      <c r="B5877">
+        <v>840</v>
+      </c>
+      <c r="C5877">
+        <v>0</v>
+      </c>
+      <c r="D5877">
+        <v>0</v>
+      </c>
+      <c r="E5877">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5878">
+      <c r="A5878" s="2">
+        <v>46139</v>
+      </c>
+      <c r="B5878">
+        <v>840</v>
+      </c>
+      <c r="C5878">
+        <v>0</v>
+      </c>
+      <c r="D5878">
+        <v>0</v>
+      </c>
+      <c r="E5878">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5879">
+      <c r="A5879" s="2">
+        <v>46139</v>
+      </c>
+      <c r="B5879">
+        <v>840</v>
+      </c>
+      <c r="C5879">
+        <v>0</v>
+      </c>
+      <c r="D5879">
+        <v>0</v>
+      </c>
+      <c r="E5879">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5880">
+      <c r="A5880" s="2">
+        <v>46139</v>
+      </c>
+      <c r="B5880">
+        <v>840</v>
+      </c>
+      <c r="C5880">
+        <v>0</v>
+      </c>
+      <c r="D5880">
+        <v>0</v>
+      </c>
+      <c r="E5880">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5881">
+      <c r="A5881" s="2">
+        <v>46139</v>
+      </c>
+      <c r="B5881">
+        <v>840</v>
+      </c>
+      <c r="C5881">
+        <v>0</v>
+      </c>
+      <c r="D5881">
+        <v>0</v>
+      </c>
+      <c r="E5881">
+        <v>4</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data-raw/resultados_supersete.xlsx
+++ b/data-raw/resultados_supersete.xlsx
@@ -355,7 +355,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E5881"/>
+  <dimension ref="A1:E5888"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" style="2" customWidth="1"/>
@@ -100348,6 +100348,125 @@
         <v>4</v>
       </c>
     </row>
+    <row r="5882">
+      <c r="A5882" s="2">
+        <v>46141</v>
+      </c>
+      <c r="B5882">
+        <v>841</v>
+      </c>
+      <c r="C5882">
+        <v>1</v>
+      </c>
+      <c r="D5882">
+        <v>7176787.87</v>
+      </c>
+      <c r="E5882">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5883">
+      <c r="A5883" s="2">
+        <v>46141</v>
+      </c>
+      <c r="B5883">
+        <v>841</v>
+      </c>
+      <c r="C5883">
+        <v>1</v>
+      </c>
+      <c r="D5883">
+        <v>7176787.87</v>
+      </c>
+      <c r="E5883">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5884">
+      <c r="A5884" s="2">
+        <v>46141</v>
+      </c>
+      <c r="B5884">
+        <v>841</v>
+      </c>
+      <c r="C5884">
+        <v>1</v>
+      </c>
+      <c r="D5884">
+        <v>7176787.87</v>
+      </c>
+      <c r="E5884">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5885">
+      <c r="A5885" s="2">
+        <v>46141</v>
+      </c>
+      <c r="B5885">
+        <v>841</v>
+      </c>
+      <c r="C5885">
+        <v>1</v>
+      </c>
+      <c r="D5885">
+        <v>7176787.87</v>
+      </c>
+      <c r="E5885">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5886">
+      <c r="A5886" s="2">
+        <v>46141</v>
+      </c>
+      <c r="B5886">
+        <v>841</v>
+      </c>
+      <c r="C5886">
+        <v>1</v>
+      </c>
+      <c r="D5886">
+        <v>7176787.87</v>
+      </c>
+      <c r="E5886">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5887">
+      <c r="A5887" s="2">
+        <v>46141</v>
+      </c>
+      <c r="B5887">
+        <v>841</v>
+      </c>
+      <c r="C5887">
+        <v>1</v>
+      </c>
+      <c r="D5887">
+        <v>7176787.87</v>
+      </c>
+      <c r="E5887">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5888">
+      <c r="A5888" s="2">
+        <v>46141</v>
+      </c>
+      <c r="B5888">
+        <v>841</v>
+      </c>
+      <c r="C5888">
+        <v>1</v>
+      </c>
+      <c r="D5888">
+        <v>7176787.87</v>
+      </c>
+      <c r="E5888">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data-raw/resultados_supersete.xlsx
+++ b/data-raw/resultados_supersete.xlsx
@@ -355,7 +355,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E5888"/>
+  <dimension ref="A1:E5895"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" style="2" customWidth="1"/>
@@ -100467,6 +100467,125 @@
         <v>7</v>
       </c>
     </row>
+    <row r="5889">
+      <c r="A5889" s="2">
+        <v>46146</v>
+      </c>
+      <c r="B5889">
+        <v>842</v>
+      </c>
+      <c r="C5889">
+        <v>0</v>
+      </c>
+      <c r="D5889">
+        <v>0</v>
+      </c>
+      <c r="E5889">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5890">
+      <c r="A5890" s="2">
+        <v>46146</v>
+      </c>
+      <c r="B5890">
+        <v>842</v>
+      </c>
+      <c r="C5890">
+        <v>0</v>
+      </c>
+      <c r="D5890">
+        <v>0</v>
+      </c>
+      <c r="E5890">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5891">
+      <c r="A5891" s="2">
+        <v>46146</v>
+      </c>
+      <c r="B5891">
+        <v>842</v>
+      </c>
+      <c r="C5891">
+        <v>0</v>
+      </c>
+      <c r="D5891">
+        <v>0</v>
+      </c>
+      <c r="E5891">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5892">
+      <c r="A5892" s="2">
+        <v>46146</v>
+      </c>
+      <c r="B5892">
+        <v>842</v>
+      </c>
+      <c r="C5892">
+        <v>0</v>
+      </c>
+      <c r="D5892">
+        <v>0</v>
+      </c>
+      <c r="E5892">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5893">
+      <c r="A5893" s="2">
+        <v>46146</v>
+      </c>
+      <c r="B5893">
+        <v>842</v>
+      </c>
+      <c r="C5893">
+        <v>0</v>
+      </c>
+      <c r="D5893">
+        <v>0</v>
+      </c>
+      <c r="E5893">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5894">
+      <c r="A5894" s="2">
+        <v>46146</v>
+      </c>
+      <c r="B5894">
+        <v>842</v>
+      </c>
+      <c r="C5894">
+        <v>0</v>
+      </c>
+      <c r="D5894">
+        <v>0</v>
+      </c>
+      <c r="E5894">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5895">
+      <c r="A5895" s="2">
+        <v>46146</v>
+      </c>
+      <c r="B5895">
+        <v>842</v>
+      </c>
+      <c r="C5895">
+        <v>0</v>
+      </c>
+      <c r="D5895">
+        <v>0</v>
+      </c>
+      <c r="E5895">
+        <v>2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data-raw/resultados_supersete.xlsx
+++ b/data-raw/resultados_supersete.xlsx
@@ -355,7 +355,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E5895"/>
+  <dimension ref="A1:E5902"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" style="2" customWidth="1"/>
@@ -100586,6 +100586,125 @@
         <v>2</v>
       </c>
     </row>
+    <row r="5896">
+      <c r="A5896" s="2">
+        <v>46148</v>
+      </c>
+      <c r="B5896">
+        <v>843</v>
+      </c>
+      <c r="C5896">
+        <v>0</v>
+      </c>
+      <c r="D5896">
+        <v>0</v>
+      </c>
+      <c r="E5896">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5897">
+      <c r="A5897" s="2">
+        <v>46148</v>
+      </c>
+      <c r="B5897">
+        <v>843</v>
+      </c>
+      <c r="C5897">
+        <v>0</v>
+      </c>
+      <c r="D5897">
+        <v>0</v>
+      </c>
+      <c r="E5897">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5898">
+      <c r="A5898" s="2">
+        <v>46148</v>
+      </c>
+      <c r="B5898">
+        <v>843</v>
+      </c>
+      <c r="C5898">
+        <v>0</v>
+      </c>
+      <c r="D5898">
+        <v>0</v>
+      </c>
+      <c r="E5898">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5899">
+      <c r="A5899" s="2">
+        <v>46148</v>
+      </c>
+      <c r="B5899">
+        <v>843</v>
+      </c>
+      <c r="C5899">
+        <v>0</v>
+      </c>
+      <c r="D5899">
+        <v>0</v>
+      </c>
+      <c r="E5899">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5900">
+      <c r="A5900" s="2">
+        <v>46148</v>
+      </c>
+      <c r="B5900">
+        <v>843</v>
+      </c>
+      <c r="C5900">
+        <v>0</v>
+      </c>
+      <c r="D5900">
+        <v>0</v>
+      </c>
+      <c r="E5900">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5901">
+      <c r="A5901" s="2">
+        <v>46148</v>
+      </c>
+      <c r="B5901">
+        <v>843</v>
+      </c>
+      <c r="C5901">
+        <v>0</v>
+      </c>
+      <c r="D5901">
+        <v>0</v>
+      </c>
+      <c r="E5901">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="5902">
+      <c r="A5902" s="2">
+        <v>46148</v>
+      </c>
+      <c r="B5902">
+        <v>843</v>
+      </c>
+      <c r="C5902">
+        <v>0</v>
+      </c>
+      <c r="D5902">
+        <v>0</v>
+      </c>
+      <c r="E5902">
+        <v>2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data-raw/resultados_supersete.xlsx
+++ b/data-raw/resultados_supersete.xlsx
@@ -355,7 +355,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E5902"/>
+  <dimension ref="A1:E5909"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" style="2" customWidth="1"/>
@@ -100705,6 +100705,125 @@
         <v>2</v>
       </c>
     </row>
+    <row r="5903">
+      <c r="A5903" s="2">
+        <v>46150</v>
+      </c>
+      <c r="B5903">
+        <v>844</v>
+      </c>
+      <c r="C5903">
+        <v>0</v>
+      </c>
+      <c r="D5903">
+        <v>0</v>
+      </c>
+      <c r="E5903">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5904">
+      <c r="A5904" s="2">
+        <v>46150</v>
+      </c>
+      <c r="B5904">
+        <v>844</v>
+      </c>
+      <c r="C5904">
+        <v>0</v>
+      </c>
+      <c r="D5904">
+        <v>0</v>
+      </c>
+      <c r="E5904">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5905">
+      <c r="A5905" s="2">
+        <v>46150</v>
+      </c>
+      <c r="B5905">
+        <v>844</v>
+      </c>
+      <c r="C5905">
+        <v>0</v>
+      </c>
+      <c r="D5905">
+        <v>0</v>
+      </c>
+      <c r="E5905">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5906">
+      <c r="A5906" s="2">
+        <v>46150</v>
+      </c>
+      <c r="B5906">
+        <v>844</v>
+      </c>
+      <c r="C5906">
+        <v>0</v>
+      </c>
+      <c r="D5906">
+        <v>0</v>
+      </c>
+      <c r="E5906">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="5907">
+      <c r="A5907" s="2">
+        <v>46150</v>
+      </c>
+      <c r="B5907">
+        <v>844</v>
+      </c>
+      <c r="C5907">
+        <v>0</v>
+      </c>
+      <c r="D5907">
+        <v>0</v>
+      </c>
+      <c r="E5907">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="5908">
+      <c r="A5908" s="2">
+        <v>46150</v>
+      </c>
+      <c r="B5908">
+        <v>844</v>
+      </c>
+      <c r="C5908">
+        <v>0</v>
+      </c>
+      <c r="D5908">
+        <v>0</v>
+      </c>
+      <c r="E5908">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5909">
+      <c r="A5909" s="2">
+        <v>46150</v>
+      </c>
+      <c r="B5909">
+        <v>844</v>
+      </c>
+      <c r="C5909">
+        <v>0</v>
+      </c>
+      <c r="D5909">
+        <v>0</v>
+      </c>
+      <c r="E5909">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data-raw/resultados_supersete.xlsx
+++ b/data-raw/resultados_supersete.xlsx
@@ -355,7 +355,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E5909"/>
+  <dimension ref="A1:E5916"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" style="2" customWidth="1"/>
@@ -100824,6 +100824,125 @@
         <v>0</v>
       </c>
     </row>
+    <row r="5910">
+      <c r="A5910" s="2">
+        <v>46153</v>
+      </c>
+      <c r="B5910">
+        <v>845</v>
+      </c>
+      <c r="C5910">
+        <v>0</v>
+      </c>
+      <c r="D5910">
+        <v>0</v>
+      </c>
+      <c r="E5910">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5911">
+      <c r="A5911" s="2">
+        <v>46153</v>
+      </c>
+      <c r="B5911">
+        <v>845</v>
+      </c>
+      <c r="C5911">
+        <v>0</v>
+      </c>
+      <c r="D5911">
+        <v>0</v>
+      </c>
+      <c r="E5911">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5912">
+      <c r="A5912" s="2">
+        <v>46153</v>
+      </c>
+      <c r="B5912">
+        <v>845</v>
+      </c>
+      <c r="C5912">
+        <v>0</v>
+      </c>
+      <c r="D5912">
+        <v>0</v>
+      </c>
+      <c r="E5912">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5913">
+      <c r="A5913" s="2">
+        <v>46153</v>
+      </c>
+      <c r="B5913">
+        <v>845</v>
+      </c>
+      <c r="C5913">
+        <v>0</v>
+      </c>
+      <c r="D5913">
+        <v>0</v>
+      </c>
+      <c r="E5913">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5914">
+      <c r="A5914" s="2">
+        <v>46153</v>
+      </c>
+      <c r="B5914">
+        <v>845</v>
+      </c>
+      <c r="C5914">
+        <v>0</v>
+      </c>
+      <c r="D5914">
+        <v>0</v>
+      </c>
+      <c r="E5914">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5915">
+      <c r="A5915" s="2">
+        <v>46153</v>
+      </c>
+      <c r="B5915">
+        <v>845</v>
+      </c>
+      <c r="C5915">
+        <v>0</v>
+      </c>
+      <c r="D5915">
+        <v>0</v>
+      </c>
+      <c r="E5915">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5916">
+      <c r="A5916" s="2">
+        <v>46153</v>
+      </c>
+      <c r="B5916">
+        <v>845</v>
+      </c>
+      <c r="C5916">
+        <v>0</v>
+      </c>
+      <c r="D5916">
+        <v>0</v>
+      </c>
+      <c r="E5916">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data-raw/resultados_supersete.xlsx
+++ b/data-raw/resultados_supersete.xlsx
@@ -355,7 +355,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E5916"/>
+  <dimension ref="A1:E5923"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" style="2" customWidth="1"/>
@@ -100943,6 +100943,125 @@
         <v>1</v>
       </c>
     </row>
+    <row r="5917">
+      <c r="A5917" s="2">
+        <v>46155</v>
+      </c>
+      <c r="B5917">
+        <v>846</v>
+      </c>
+      <c r="C5917">
+        <v>0</v>
+      </c>
+      <c r="D5917">
+        <v>0</v>
+      </c>
+      <c r="E5917">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5918">
+      <c r="A5918" s="2">
+        <v>46155</v>
+      </c>
+      <c r="B5918">
+        <v>846</v>
+      </c>
+      <c r="C5918">
+        <v>0</v>
+      </c>
+      <c r="D5918">
+        <v>0</v>
+      </c>
+      <c r="E5918">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5919">
+      <c r="A5919" s="2">
+        <v>46155</v>
+      </c>
+      <c r="B5919">
+        <v>846</v>
+      </c>
+      <c r="C5919">
+        <v>0</v>
+      </c>
+      <c r="D5919">
+        <v>0</v>
+      </c>
+      <c r="E5919">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5920">
+      <c r="A5920" s="2">
+        <v>46155</v>
+      </c>
+      <c r="B5920">
+        <v>846</v>
+      </c>
+      <c r="C5920">
+        <v>0</v>
+      </c>
+      <c r="D5920">
+        <v>0</v>
+      </c>
+      <c r="E5920">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5921">
+      <c r="A5921" s="2">
+        <v>46155</v>
+      </c>
+      <c r="B5921">
+        <v>846</v>
+      </c>
+      <c r="C5921">
+        <v>0</v>
+      </c>
+      <c r="D5921">
+        <v>0</v>
+      </c>
+      <c r="E5921">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5922">
+      <c r="A5922" s="2">
+        <v>46155</v>
+      </c>
+      <c r="B5922">
+        <v>846</v>
+      </c>
+      <c r="C5922">
+        <v>0</v>
+      </c>
+      <c r="D5922">
+        <v>0</v>
+      </c>
+      <c r="E5922">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5923">
+      <c r="A5923" s="2">
+        <v>46155</v>
+      </c>
+      <c r="B5923">
+        <v>846</v>
+      </c>
+      <c r="C5923">
+        <v>0</v>
+      </c>
+      <c r="D5923">
+        <v>0</v>
+      </c>
+      <c r="E5923">
+        <v>5</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data-raw/resultados_supersete.xlsx
+++ b/data-raw/resultados_supersete.xlsx
@@ -355,7 +355,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E5923"/>
+  <dimension ref="A1:E5930"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" style="2" customWidth="1"/>
@@ -101062,6 +101062,125 @@
         <v>5</v>
       </c>
     </row>
+    <row r="5924">
+      <c r="A5924" s="2">
+        <v>46157</v>
+      </c>
+      <c r="B5924">
+        <v>847</v>
+      </c>
+      <c r="C5924">
+        <v>0</v>
+      </c>
+      <c r="D5924">
+        <v>0</v>
+      </c>
+      <c r="E5924">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5925">
+      <c r="A5925" s="2">
+        <v>46157</v>
+      </c>
+      <c r="B5925">
+        <v>847</v>
+      </c>
+      <c r="C5925">
+        <v>0</v>
+      </c>
+      <c r="D5925">
+        <v>0</v>
+      </c>
+      <c r="E5925">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5926">
+      <c r="A5926" s="2">
+        <v>46157</v>
+      </c>
+      <c r="B5926">
+        <v>847</v>
+      </c>
+      <c r="C5926">
+        <v>0</v>
+      </c>
+      <c r="D5926">
+        <v>0</v>
+      </c>
+      <c r="E5926">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5927">
+      <c r="A5927" s="2">
+        <v>46157</v>
+      </c>
+      <c r="B5927">
+        <v>847</v>
+      </c>
+      <c r="C5927">
+        <v>0</v>
+      </c>
+      <c r="D5927">
+        <v>0</v>
+      </c>
+      <c r="E5927">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5928">
+      <c r="A5928" s="2">
+        <v>46157</v>
+      </c>
+      <c r="B5928">
+        <v>847</v>
+      </c>
+      <c r="C5928">
+        <v>0</v>
+      </c>
+      <c r="D5928">
+        <v>0</v>
+      </c>
+      <c r="E5928">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5929">
+      <c r="A5929" s="2">
+        <v>46157</v>
+      </c>
+      <c r="B5929">
+        <v>847</v>
+      </c>
+      <c r="C5929">
+        <v>0</v>
+      </c>
+      <c r="D5929">
+        <v>0</v>
+      </c>
+      <c r="E5929">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5930">
+      <c r="A5930" s="2">
+        <v>46157</v>
+      </c>
+      <c r="B5930">
+        <v>847</v>
+      </c>
+      <c r="C5930">
+        <v>0</v>
+      </c>
+      <c r="D5930">
+        <v>0</v>
+      </c>
+      <c r="E5930">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data-raw/resultados_supersete.xlsx
+++ b/data-raw/resultados_supersete.xlsx
@@ -355,7 +355,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E5930"/>
+  <dimension ref="A1:E5937"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" style="2" customWidth="1"/>
@@ -101181,6 +101181,125 @@
         <v>1</v>
       </c>
     </row>
+    <row r="5931">
+      <c r="A5931" s="2">
+        <v>46160</v>
+      </c>
+      <c r="B5931">
+        <v>848</v>
+      </c>
+      <c r="C5931">
+        <v>0</v>
+      </c>
+      <c r="D5931">
+        <v>0</v>
+      </c>
+      <c r="E5931">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5932">
+      <c r="A5932" s="2">
+        <v>46160</v>
+      </c>
+      <c r="B5932">
+        <v>848</v>
+      </c>
+      <c r="C5932">
+        <v>0</v>
+      </c>
+      <c r="D5932">
+        <v>0</v>
+      </c>
+      <c r="E5932">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5933">
+      <c r="A5933" s="2">
+        <v>46160</v>
+      </c>
+      <c r="B5933">
+        <v>848</v>
+      </c>
+      <c r="C5933">
+        <v>0</v>
+      </c>
+      <c r="D5933">
+        <v>0</v>
+      </c>
+      <c r="E5933">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5934">
+      <c r="A5934" s="2">
+        <v>46160</v>
+      </c>
+      <c r="B5934">
+        <v>848</v>
+      </c>
+      <c r="C5934">
+        <v>0</v>
+      </c>
+      <c r="D5934">
+        <v>0</v>
+      </c>
+      <c r="E5934">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5935">
+      <c r="A5935" s="2">
+        <v>46160</v>
+      </c>
+      <c r="B5935">
+        <v>848</v>
+      </c>
+      <c r="C5935">
+        <v>0</v>
+      </c>
+      <c r="D5935">
+        <v>0</v>
+      </c>
+      <c r="E5935">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5936">
+      <c r="A5936" s="2">
+        <v>46160</v>
+      </c>
+      <c r="B5936">
+        <v>848</v>
+      </c>
+      <c r="C5936">
+        <v>0</v>
+      </c>
+      <c r="D5936">
+        <v>0</v>
+      </c>
+      <c r="E5936">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5937">
+      <c r="A5937" s="2">
+        <v>46160</v>
+      </c>
+      <c r="B5937">
+        <v>848</v>
+      </c>
+      <c r="C5937">
+        <v>0</v>
+      </c>
+      <c r="D5937">
+        <v>0</v>
+      </c>
+      <c r="E5937">
+        <v>2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data-raw/resultados_supersete.xlsx
+++ b/data-raw/resultados_supersete.xlsx
@@ -355,7 +355,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E5937"/>
+  <dimension ref="A1:E5944"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" style="2" customWidth="1"/>
@@ -101300,6 +101300,125 @@
         <v>2</v>
       </c>
     </row>
+    <row r="5938">
+      <c r="A5938" s="2">
+        <v>46162</v>
+      </c>
+      <c r="B5938">
+        <v>849</v>
+      </c>
+      <c r="C5938">
+        <v>0</v>
+      </c>
+      <c r="D5938">
+        <v>0</v>
+      </c>
+      <c r="E5938">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="5939">
+      <c r="A5939" s="2">
+        <v>46162</v>
+      </c>
+      <c r="B5939">
+        <v>849</v>
+      </c>
+      <c r="C5939">
+        <v>0</v>
+      </c>
+      <c r="D5939">
+        <v>0</v>
+      </c>
+      <c r="E5939">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5940">
+      <c r="A5940" s="2">
+        <v>46162</v>
+      </c>
+      <c r="B5940">
+        <v>849</v>
+      </c>
+      <c r="C5940">
+        <v>0</v>
+      </c>
+      <c r="D5940">
+        <v>0</v>
+      </c>
+      <c r="E5940">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5941">
+      <c r="A5941" s="2">
+        <v>46162</v>
+      </c>
+      <c r="B5941">
+        <v>849</v>
+      </c>
+      <c r="C5941">
+        <v>0</v>
+      </c>
+      <c r="D5941">
+        <v>0</v>
+      </c>
+      <c r="E5941">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5942">
+      <c r="A5942" s="2">
+        <v>46162</v>
+      </c>
+      <c r="B5942">
+        <v>849</v>
+      </c>
+      <c r="C5942">
+        <v>0</v>
+      </c>
+      <c r="D5942">
+        <v>0</v>
+      </c>
+      <c r="E5942">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5943">
+      <c r="A5943" s="2">
+        <v>46162</v>
+      </c>
+      <c r="B5943">
+        <v>849</v>
+      </c>
+      <c r="C5943">
+        <v>0</v>
+      </c>
+      <c r="D5943">
+        <v>0</v>
+      </c>
+      <c r="E5943">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5944">
+      <c r="A5944" s="2">
+        <v>46162</v>
+      </c>
+      <c r="B5944">
+        <v>849</v>
+      </c>
+      <c r="C5944">
+        <v>0</v>
+      </c>
+      <c r="D5944">
+        <v>0</v>
+      </c>
+      <c r="E5944">
+        <v>5</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data-raw/resultados_supersete.xlsx
+++ b/data-raw/resultados_supersete.xlsx
@@ -355,7 +355,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E5944"/>
+  <dimension ref="A1:E5951"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" style="2" customWidth="1"/>
@@ -101419,6 +101419,125 @@
         <v>5</v>
       </c>
     </row>
+    <row r="5945">
+      <c r="A5945" s="2">
+        <v>46164</v>
+      </c>
+      <c r="B5945">
+        <v>850</v>
+      </c>
+      <c r="C5945">
+        <v>0</v>
+      </c>
+      <c r="D5945">
+        <v>0</v>
+      </c>
+      <c r="E5945">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5946">
+      <c r="A5946" s="2">
+        <v>46164</v>
+      </c>
+      <c r="B5946">
+        <v>850</v>
+      </c>
+      <c r="C5946">
+        <v>0</v>
+      </c>
+      <c r="D5946">
+        <v>0</v>
+      </c>
+      <c r="E5946">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5947">
+      <c r="A5947" s="2">
+        <v>46164</v>
+      </c>
+      <c r="B5947">
+        <v>850</v>
+      </c>
+      <c r="C5947">
+        <v>0</v>
+      </c>
+      <c r="D5947">
+        <v>0</v>
+      </c>
+      <c r="E5947">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5948">
+      <c r="A5948" s="2">
+        <v>46164</v>
+      </c>
+      <c r="B5948">
+        <v>850</v>
+      </c>
+      <c r="C5948">
+        <v>0</v>
+      </c>
+      <c r="D5948">
+        <v>0</v>
+      </c>
+      <c r="E5948">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5949">
+      <c r="A5949" s="2">
+        <v>46164</v>
+      </c>
+      <c r="B5949">
+        <v>850</v>
+      </c>
+      <c r="C5949">
+        <v>0</v>
+      </c>
+      <c r="D5949">
+        <v>0</v>
+      </c>
+      <c r="E5949">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5950">
+      <c r="A5950" s="2">
+        <v>46164</v>
+      </c>
+      <c r="B5950">
+        <v>850</v>
+      </c>
+      <c r="C5950">
+        <v>0</v>
+      </c>
+      <c r="D5950">
+        <v>0</v>
+      </c>
+      <c r="E5950">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5951">
+      <c r="A5951" s="2">
+        <v>46164</v>
+      </c>
+      <c r="B5951">
+        <v>850</v>
+      </c>
+      <c r="C5951">
+        <v>0</v>
+      </c>
+      <c r="D5951">
+        <v>0</v>
+      </c>
+      <c r="E5951">
+        <v>3</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data-raw/resultados_supersete.xlsx
+++ b/data-raw/resultados_supersete.xlsx
@@ -355,7 +355,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E5951"/>
+  <dimension ref="A1:E5958"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" style="2" customWidth="1"/>
@@ -101538,6 +101538,125 @@
         <v>3</v>
       </c>
     </row>
+    <row r="5952">
+      <c r="A5952" s="2">
+        <v>46167</v>
+      </c>
+      <c r="B5952">
+        <v>851</v>
+      </c>
+      <c r="C5952">
+        <v>0</v>
+      </c>
+      <c r="D5952">
+        <v>0</v>
+      </c>
+      <c r="E5952">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="5953">
+      <c r="A5953" s="2">
+        <v>46167</v>
+      </c>
+      <c r="B5953">
+        <v>851</v>
+      </c>
+      <c r="C5953">
+        <v>0</v>
+      </c>
+      <c r="D5953">
+        <v>0</v>
+      </c>
+      <c r="E5953">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5954">
+      <c r="A5954" s="2">
+        <v>46167</v>
+      </c>
+      <c r="B5954">
+        <v>851</v>
+      </c>
+      <c r="C5954">
+        <v>0</v>
+      </c>
+      <c r="D5954">
+        <v>0</v>
+      </c>
+      <c r="E5954">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5955">
+      <c r="A5955" s="2">
+        <v>46167</v>
+      </c>
+      <c r="B5955">
+        <v>851</v>
+      </c>
+      <c r="C5955">
+        <v>0</v>
+      </c>
+      <c r="D5955">
+        <v>0</v>
+      </c>
+      <c r="E5955">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5956">
+      <c r="A5956" s="2">
+        <v>46167</v>
+      </c>
+      <c r="B5956">
+        <v>851</v>
+      </c>
+      <c r="C5956">
+        <v>0</v>
+      </c>
+      <c r="D5956">
+        <v>0</v>
+      </c>
+      <c r="E5956">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="5957">
+      <c r="A5957" s="2">
+        <v>46167</v>
+      </c>
+      <c r="B5957">
+        <v>851</v>
+      </c>
+      <c r="C5957">
+        <v>0</v>
+      </c>
+      <c r="D5957">
+        <v>0</v>
+      </c>
+      <c r="E5957">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5958">
+      <c r="A5958" s="2">
+        <v>46167</v>
+      </c>
+      <c r="B5958">
+        <v>851</v>
+      </c>
+      <c r="C5958">
+        <v>0</v>
+      </c>
+      <c r="D5958">
+        <v>0</v>
+      </c>
+      <c r="E5958">
+        <v>6</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data-raw/resultados_supersete.xlsx
+++ b/data-raw/resultados_supersete.xlsx
@@ -355,7 +355,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E5958"/>
+  <dimension ref="A1:E5965"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" style="2" customWidth="1"/>
@@ -101657,6 +101657,125 @@
         <v>6</v>
       </c>
     </row>
+    <row r="5959">
+      <c r="A5959" s="2">
+        <v>46169</v>
+      </c>
+      <c r="B5959">
+        <v>852</v>
+      </c>
+      <c r="C5959">
+        <v>0</v>
+      </c>
+      <c r="D5959">
+        <v>0</v>
+      </c>
+      <c r="E5959">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5960">
+      <c r="A5960" s="2">
+        <v>46169</v>
+      </c>
+      <c r="B5960">
+        <v>852</v>
+      </c>
+      <c r="C5960">
+        <v>0</v>
+      </c>
+      <c r="D5960">
+        <v>0</v>
+      </c>
+      <c r="E5960">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5961">
+      <c r="A5961" s="2">
+        <v>46169</v>
+      </c>
+      <c r="B5961">
+        <v>852</v>
+      </c>
+      <c r="C5961">
+        <v>0</v>
+      </c>
+      <c r="D5961">
+        <v>0</v>
+      </c>
+      <c r="E5961">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5962">
+      <c r="A5962" s="2">
+        <v>46169</v>
+      </c>
+      <c r="B5962">
+        <v>852</v>
+      </c>
+      <c r="C5962">
+        <v>0</v>
+      </c>
+      <c r="D5962">
+        <v>0</v>
+      </c>
+      <c r="E5962">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5963">
+      <c r="A5963" s="2">
+        <v>46169</v>
+      </c>
+      <c r="B5963">
+        <v>852</v>
+      </c>
+      <c r="C5963">
+        <v>0</v>
+      </c>
+      <c r="D5963">
+        <v>0</v>
+      </c>
+      <c r="E5963">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5964">
+      <c r="A5964" s="2">
+        <v>46169</v>
+      </c>
+      <c r="B5964">
+        <v>852</v>
+      </c>
+      <c r="C5964">
+        <v>0</v>
+      </c>
+      <c r="D5964">
+        <v>0</v>
+      </c>
+      <c r="E5964">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5965">
+      <c r="A5965" s="2">
+        <v>46169</v>
+      </c>
+      <c r="B5965">
+        <v>852</v>
+      </c>
+      <c r="C5965">
+        <v>0</v>
+      </c>
+      <c r="D5965">
+        <v>0</v>
+      </c>
+      <c r="E5965">
+        <v>5</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data-raw/resultados_supersete.xlsx
+++ b/data-raw/resultados_supersete.xlsx
@@ -355,7 +355,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E5965"/>
+  <dimension ref="A1:E5972"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" style="2" customWidth="1"/>
@@ -101776,6 +101776,125 @@
         <v>5</v>
       </c>
     </row>
+    <row r="5966">
+      <c r="A5966" s="2">
+        <v>46171</v>
+      </c>
+      <c r="B5966">
+        <v>853</v>
+      </c>
+      <c r="C5966">
+        <v>0</v>
+      </c>
+      <c r="D5966">
+        <v>0</v>
+      </c>
+      <c r="E5966">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5967">
+      <c r="A5967" s="2">
+        <v>46171</v>
+      </c>
+      <c r="B5967">
+        <v>853</v>
+      </c>
+      <c r="C5967">
+        <v>0</v>
+      </c>
+      <c r="D5967">
+        <v>0</v>
+      </c>
+      <c r="E5967">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5968">
+      <c r="A5968" s="2">
+        <v>46171</v>
+      </c>
+      <c r="B5968">
+        <v>853</v>
+      </c>
+      <c r="C5968">
+        <v>0</v>
+      </c>
+      <c r="D5968">
+        <v>0</v>
+      </c>
+      <c r="E5968">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5969">
+      <c r="A5969" s="2">
+        <v>46171</v>
+      </c>
+      <c r="B5969">
+        <v>853</v>
+      </c>
+      <c r="C5969">
+        <v>0</v>
+      </c>
+      <c r="D5969">
+        <v>0</v>
+      </c>
+      <c r="E5969">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5970">
+      <c r="A5970" s="2">
+        <v>46171</v>
+      </c>
+      <c r="B5970">
+        <v>853</v>
+      </c>
+      <c r="C5970">
+        <v>0</v>
+      </c>
+      <c r="D5970">
+        <v>0</v>
+      </c>
+      <c r="E5970">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5971">
+      <c r="A5971" s="2">
+        <v>46171</v>
+      </c>
+      <c r="B5971">
+        <v>853</v>
+      </c>
+      <c r="C5971">
+        <v>0</v>
+      </c>
+      <c r="D5971">
+        <v>0</v>
+      </c>
+      <c r="E5971">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5972">
+      <c r="A5972" s="2">
+        <v>46171</v>
+      </c>
+      <c r="B5972">
+        <v>853</v>
+      </c>
+      <c r="C5972">
+        <v>0</v>
+      </c>
+      <c r="D5972">
+        <v>0</v>
+      </c>
+      <c r="E5972">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data-raw/resultados_supersete.xlsx
+++ b/data-raw/resultados_supersete.xlsx
@@ -355,7 +355,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E5972"/>
+  <dimension ref="A1:E5979"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" style="2" customWidth="1"/>
@@ -101895,6 +101895,125 @@
         <v>8</v>
       </c>
     </row>
+    <row r="5973">
+      <c r="A5973" s="2">
+        <v>46174</v>
+      </c>
+      <c r="B5973">
+        <v>854</v>
+      </c>
+      <c r="C5973">
+        <v>0</v>
+      </c>
+      <c r="D5973">
+        <v>0</v>
+      </c>
+      <c r="E5973">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5974">
+      <c r="A5974" s="2">
+        <v>46174</v>
+      </c>
+      <c r="B5974">
+        <v>854</v>
+      </c>
+      <c r="C5974">
+        <v>0</v>
+      </c>
+      <c r="D5974">
+        <v>0</v>
+      </c>
+      <c r="E5974">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5975">
+      <c r="A5975" s="2">
+        <v>46174</v>
+      </c>
+      <c r="B5975">
+        <v>854</v>
+      </c>
+      <c r="C5975">
+        <v>0</v>
+      </c>
+      <c r="D5975">
+        <v>0</v>
+      </c>
+      <c r="E5975">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="5976">
+      <c r="A5976" s="2">
+        <v>46174</v>
+      </c>
+      <c r="B5976">
+        <v>854</v>
+      </c>
+      <c r="C5976">
+        <v>0</v>
+      </c>
+      <c r="D5976">
+        <v>0</v>
+      </c>
+      <c r="E5976">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5977">
+      <c r="A5977" s="2">
+        <v>46174</v>
+      </c>
+      <c r="B5977">
+        <v>854</v>
+      </c>
+      <c r="C5977">
+        <v>0</v>
+      </c>
+      <c r="D5977">
+        <v>0</v>
+      </c>
+      <c r="E5977">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5978">
+      <c r="A5978" s="2">
+        <v>46174</v>
+      </c>
+      <c r="B5978">
+        <v>854</v>
+      </c>
+      <c r="C5978">
+        <v>0</v>
+      </c>
+      <c r="D5978">
+        <v>0</v>
+      </c>
+      <c r="E5978">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5979">
+      <c r="A5979" s="2">
+        <v>46174</v>
+      </c>
+      <c r="B5979">
+        <v>854</v>
+      </c>
+      <c r="C5979">
+        <v>0</v>
+      </c>
+      <c r="D5979">
+        <v>0</v>
+      </c>
+      <c r="E5979">
+        <v>4</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data-raw/resultados_supersete.xlsx
+++ b/data-raw/resultados_supersete.xlsx
@@ -355,7 +355,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E5979"/>
+  <dimension ref="A1:E5986"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" style="2" customWidth="1"/>
@@ -102014,6 +102014,125 @@
         <v>4</v>
       </c>
     </row>
+    <row r="5980">
+      <c r="A5980" s="2">
+        <v>46176</v>
+      </c>
+      <c r="B5980">
+        <v>855</v>
+      </c>
+      <c r="C5980">
+        <v>0</v>
+      </c>
+      <c r="D5980">
+        <v>0</v>
+      </c>
+      <c r="E5980">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5981">
+      <c r="A5981" s="2">
+        <v>46176</v>
+      </c>
+      <c r="B5981">
+        <v>855</v>
+      </c>
+      <c r="C5981">
+        <v>0</v>
+      </c>
+      <c r="D5981">
+        <v>0</v>
+      </c>
+      <c r="E5981">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5982">
+      <c r="A5982" s="2">
+        <v>46176</v>
+      </c>
+      <c r="B5982">
+        <v>855</v>
+      </c>
+      <c r="C5982">
+        <v>0</v>
+      </c>
+      <c r="D5982">
+        <v>0</v>
+      </c>
+      <c r="E5982">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5983">
+      <c r="A5983" s="2">
+        <v>46176</v>
+      </c>
+      <c r="B5983">
+        <v>855</v>
+      </c>
+      <c r="C5983">
+        <v>0</v>
+      </c>
+      <c r="D5983">
+        <v>0</v>
+      </c>
+      <c r="E5983">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5984">
+      <c r="A5984" s="2">
+        <v>46176</v>
+      </c>
+      <c r="B5984">
+        <v>855</v>
+      </c>
+      <c r="C5984">
+        <v>0</v>
+      </c>
+      <c r="D5984">
+        <v>0</v>
+      </c>
+      <c r="E5984">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5985">
+      <c r="A5985" s="2">
+        <v>46176</v>
+      </c>
+      <c r="B5985">
+        <v>855</v>
+      </c>
+      <c r="C5985">
+        <v>0</v>
+      </c>
+      <c r="D5985">
+        <v>0</v>
+      </c>
+      <c r="E5985">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5986">
+      <c r="A5986" s="2">
+        <v>46176</v>
+      </c>
+      <c r="B5986">
+        <v>855</v>
+      </c>
+      <c r="C5986">
+        <v>0</v>
+      </c>
+      <c r="D5986">
+        <v>0</v>
+      </c>
+      <c r="E5986">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data-raw/resultados_supersete.xlsx
+++ b/data-raw/resultados_supersete.xlsx
@@ -355,7 +355,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E5986"/>
+  <dimension ref="A1:E5993"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" style="2" customWidth="1"/>
@@ -102133,6 +102133,125 @@
         <v>0</v>
       </c>
     </row>
+    <row r="5987">
+      <c r="A5987" s="2">
+        <v>46178</v>
+      </c>
+      <c r="B5987">
+        <v>856</v>
+      </c>
+      <c r="C5987">
+        <v>0</v>
+      </c>
+      <c r="D5987">
+        <v>0</v>
+      </c>
+      <c r="E5987">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5988">
+      <c r="A5988" s="2">
+        <v>46178</v>
+      </c>
+      <c r="B5988">
+        <v>856</v>
+      </c>
+      <c r="C5988">
+        <v>0</v>
+      </c>
+      <c r="D5988">
+        <v>0</v>
+      </c>
+      <c r="E5988">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5989">
+      <c r="A5989" s="2">
+        <v>46178</v>
+      </c>
+      <c r="B5989">
+        <v>856</v>
+      </c>
+      <c r="C5989">
+        <v>0</v>
+      </c>
+      <c r="D5989">
+        <v>0</v>
+      </c>
+      <c r="E5989">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5990">
+      <c r="A5990" s="2">
+        <v>46178</v>
+      </c>
+      <c r="B5990">
+        <v>856</v>
+      </c>
+      <c r="C5990">
+        <v>0</v>
+      </c>
+      <c r="D5990">
+        <v>0</v>
+      </c>
+      <c r="E5990">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5991">
+      <c r="A5991" s="2">
+        <v>46178</v>
+      </c>
+      <c r="B5991">
+        <v>856</v>
+      </c>
+      <c r="C5991">
+        <v>0</v>
+      </c>
+      <c r="D5991">
+        <v>0</v>
+      </c>
+      <c r="E5991">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5992">
+      <c r="A5992" s="2">
+        <v>46178</v>
+      </c>
+      <c r="B5992">
+        <v>856</v>
+      </c>
+      <c r="C5992">
+        <v>0</v>
+      </c>
+      <c r="D5992">
+        <v>0</v>
+      </c>
+      <c r="E5992">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5993">
+      <c r="A5993" s="2">
+        <v>46178</v>
+      </c>
+      <c r="B5993">
+        <v>856</v>
+      </c>
+      <c r="C5993">
+        <v>0</v>
+      </c>
+      <c r="D5993">
+        <v>0</v>
+      </c>
+      <c r="E5993">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data-raw/resultados_supersete.xlsx
+++ b/data-raw/resultados_supersete.xlsx
@@ -355,7 +355,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E5993"/>
+  <dimension ref="A1:E6000"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" style="2" customWidth="1"/>
@@ -102252,6 +102252,125 @@
         <v>1</v>
       </c>
     </row>
+    <row r="5994">
+      <c r="A5994" s="2">
+        <v>46181</v>
+      </c>
+      <c r="B5994">
+        <v>857</v>
+      </c>
+      <c r="C5994">
+        <v>0</v>
+      </c>
+      <c r="D5994">
+        <v>0</v>
+      </c>
+      <c r="E5994">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5995">
+      <c r="A5995" s="2">
+        <v>46181</v>
+      </c>
+      <c r="B5995">
+        <v>857</v>
+      </c>
+      <c r="C5995">
+        <v>0</v>
+      </c>
+      <c r="D5995">
+        <v>0</v>
+      </c>
+      <c r="E5995">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5996">
+      <c r="A5996" s="2">
+        <v>46181</v>
+      </c>
+      <c r="B5996">
+        <v>857</v>
+      </c>
+      <c r="C5996">
+        <v>0</v>
+      </c>
+      <c r="D5996">
+        <v>0</v>
+      </c>
+      <c r="E5996">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5997">
+      <c r="A5997" s="2">
+        <v>46181</v>
+      </c>
+      <c r="B5997">
+        <v>857</v>
+      </c>
+      <c r="C5997">
+        <v>0</v>
+      </c>
+      <c r="D5997">
+        <v>0</v>
+      </c>
+      <c r="E5997">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5998">
+      <c r="A5998" s="2">
+        <v>46181</v>
+      </c>
+      <c r="B5998">
+        <v>857</v>
+      </c>
+      <c r="C5998">
+        <v>0</v>
+      </c>
+      <c r="D5998">
+        <v>0</v>
+      </c>
+      <c r="E5998">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5999">
+      <c r="A5999" s="2">
+        <v>46181</v>
+      </c>
+      <c r="B5999">
+        <v>857</v>
+      </c>
+      <c r="C5999">
+        <v>0</v>
+      </c>
+      <c r="D5999">
+        <v>0</v>
+      </c>
+      <c r="E5999">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6000">
+      <c r="A6000" s="2">
+        <v>46181</v>
+      </c>
+      <c r="B6000">
+        <v>857</v>
+      </c>
+      <c r="C6000">
+        <v>0</v>
+      </c>
+      <c r="D6000">
+        <v>0</v>
+      </c>
+      <c r="E6000">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data-raw/resultados_supersete.xlsx
+++ b/data-raw/resultados_supersete.xlsx
@@ -355,7 +355,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E6000"/>
+  <dimension ref="A1:E6007"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" style="2" customWidth="1"/>
@@ -102371,6 +102371,125 @@
         <v>7</v>
       </c>
     </row>
+    <row r="6001">
+      <c r="A6001" s="2">
+        <v>46183</v>
+      </c>
+      <c r="B6001">
+        <v>858</v>
+      </c>
+      <c r="C6001">
+        <v>0</v>
+      </c>
+      <c r="D6001">
+        <v>0</v>
+      </c>
+      <c r="E6001">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6002">
+      <c r="A6002" s="2">
+        <v>46183</v>
+      </c>
+      <c r="B6002">
+        <v>858</v>
+      </c>
+      <c r="C6002">
+        <v>0</v>
+      </c>
+      <c r="D6002">
+        <v>0</v>
+      </c>
+      <c r="E6002">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6003">
+      <c r="A6003" s="2">
+        <v>46183</v>
+      </c>
+      <c r="B6003">
+        <v>858</v>
+      </c>
+      <c r="C6003">
+        <v>0</v>
+      </c>
+      <c r="D6003">
+        <v>0</v>
+      </c>
+      <c r="E6003">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6004">
+      <c r="A6004" s="2">
+        <v>46183</v>
+      </c>
+      <c r="B6004">
+        <v>858</v>
+      </c>
+      <c r="C6004">
+        <v>0</v>
+      </c>
+      <c r="D6004">
+        <v>0</v>
+      </c>
+      <c r="E6004">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6005">
+      <c r="A6005" s="2">
+        <v>46183</v>
+      </c>
+      <c r="B6005">
+        <v>858</v>
+      </c>
+      <c r="C6005">
+        <v>0</v>
+      </c>
+      <c r="D6005">
+        <v>0</v>
+      </c>
+      <c r="E6005">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6006">
+      <c r="A6006" s="2">
+        <v>46183</v>
+      </c>
+      <c r="B6006">
+        <v>858</v>
+      </c>
+      <c r="C6006">
+        <v>0</v>
+      </c>
+      <c r="D6006">
+        <v>0</v>
+      </c>
+      <c r="E6006">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6007">
+      <c r="A6007" s="2">
+        <v>46183</v>
+      </c>
+      <c r="B6007">
+        <v>858</v>
+      </c>
+      <c r="C6007">
+        <v>0</v>
+      </c>
+      <c r="D6007">
+        <v>0</v>
+      </c>
+      <c r="E6007">
+        <v>6</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data-raw/resultados_supersete.xlsx
+++ b/data-raw/resultados_supersete.xlsx
@@ -355,7 +355,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E6007"/>
+  <dimension ref="A1:E6014"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" style="2" customWidth="1"/>
@@ -102490,6 +102490,125 @@
         <v>6</v>
       </c>
     </row>
+    <row r="6008">
+      <c r="A6008" s="2">
+        <v>46185</v>
+      </c>
+      <c r="B6008">
+        <v>859</v>
+      </c>
+      <c r="C6008">
+        <v>0</v>
+      </c>
+      <c r="D6008">
+        <v>0</v>
+      </c>
+      <c r="E6008">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6009">
+      <c r="A6009" s="2">
+        <v>46185</v>
+      </c>
+      <c r="B6009">
+        <v>859</v>
+      </c>
+      <c r="C6009">
+        <v>0</v>
+      </c>
+      <c r="D6009">
+        <v>0</v>
+      </c>
+      <c r="E6009">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6010">
+      <c r="A6010" s="2">
+        <v>46185</v>
+      </c>
+      <c r="B6010">
+        <v>859</v>
+      </c>
+      <c r="C6010">
+        <v>0</v>
+      </c>
+      <c r="D6010">
+        <v>0</v>
+      </c>
+      <c r="E6010">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6011">
+      <c r="A6011" s="2">
+        <v>46185</v>
+      </c>
+      <c r="B6011">
+        <v>859</v>
+      </c>
+      <c r="C6011">
+        <v>0</v>
+      </c>
+      <c r="D6011">
+        <v>0</v>
+      </c>
+      <c r="E6011">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6012">
+      <c r="A6012" s="2">
+        <v>46185</v>
+      </c>
+      <c r="B6012">
+        <v>859</v>
+      </c>
+      <c r="C6012">
+        <v>0</v>
+      </c>
+      <c r="D6012">
+        <v>0</v>
+      </c>
+      <c r="E6012">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6013">
+      <c r="A6013" s="2">
+        <v>46185</v>
+      </c>
+      <c r="B6013">
+        <v>859</v>
+      </c>
+      <c r="C6013">
+        <v>0</v>
+      </c>
+      <c r="D6013">
+        <v>0</v>
+      </c>
+      <c r="E6013">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6014">
+      <c r="A6014" s="2">
+        <v>46185</v>
+      </c>
+      <c r="B6014">
+        <v>859</v>
+      </c>
+      <c r="C6014">
+        <v>0</v>
+      </c>
+      <c r="D6014">
+        <v>0</v>
+      </c>
+      <c r="E6014">
+        <v>3</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data-raw/resultados_supersete.xlsx
+++ b/data-raw/resultados_supersete.xlsx
@@ -355,7 +355,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E6014"/>
+  <dimension ref="A1:E6021"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" style="2" customWidth="1"/>
@@ -102609,6 +102609,125 @@
         <v>3</v>
       </c>
     </row>
+    <row r="6015">
+      <c r="A6015" s="2">
+        <v>46188</v>
+      </c>
+      <c r="B6015">
+        <v>860</v>
+      </c>
+      <c r="C6015">
+        <v>0</v>
+      </c>
+      <c r="D6015">
+        <v>0</v>
+      </c>
+      <c r="E6015">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6016">
+      <c r="A6016" s="2">
+        <v>46188</v>
+      </c>
+      <c r="B6016">
+        <v>860</v>
+      </c>
+      <c r="C6016">
+        <v>0</v>
+      </c>
+      <c r="D6016">
+        <v>0</v>
+      </c>
+      <c r="E6016">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6017">
+      <c r="A6017" s="2">
+        <v>46188</v>
+      </c>
+      <c r="B6017">
+        <v>860</v>
+      </c>
+      <c r="C6017">
+        <v>0</v>
+      </c>
+      <c r="D6017">
+        <v>0</v>
+      </c>
+      <c r="E6017">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6018">
+      <c r="A6018" s="2">
+        <v>46188</v>
+      </c>
+      <c r="B6018">
+        <v>860</v>
+      </c>
+      <c r="C6018">
+        <v>0</v>
+      </c>
+      <c r="D6018">
+        <v>0</v>
+      </c>
+      <c r="E6018">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6019">
+      <c r="A6019" s="2">
+        <v>46188</v>
+      </c>
+      <c r="B6019">
+        <v>860</v>
+      </c>
+      <c r="C6019">
+        <v>0</v>
+      </c>
+      <c r="D6019">
+        <v>0</v>
+      </c>
+      <c r="E6019">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6020">
+      <c r="A6020" s="2">
+        <v>46188</v>
+      </c>
+      <c r="B6020">
+        <v>860</v>
+      </c>
+      <c r="C6020">
+        <v>0</v>
+      </c>
+      <c r="D6020">
+        <v>0</v>
+      </c>
+      <c r="E6020">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6021">
+      <c r="A6021" s="2">
+        <v>46188</v>
+      </c>
+      <c r="B6021">
+        <v>860</v>
+      </c>
+      <c r="C6021">
+        <v>0</v>
+      </c>
+      <c r="D6021">
+        <v>0</v>
+      </c>
+      <c r="E6021">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data-raw/resultados_supersete.xlsx
+++ b/data-raw/resultados_supersete.xlsx
@@ -355,7 +355,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E6021"/>
+  <dimension ref="A1:E6028"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" style="2" customWidth="1"/>
@@ -102728,6 +102728,125 @@
         <v>1</v>
       </c>
     </row>
+    <row r="6022">
+      <c r="A6022" s="2">
+        <v>46190</v>
+      </c>
+      <c r="B6022">
+        <v>861</v>
+      </c>
+      <c r="C6022">
+        <v>0</v>
+      </c>
+      <c r="D6022">
+        <v>0</v>
+      </c>
+      <c r="E6022">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6023">
+      <c r="A6023" s="2">
+        <v>46190</v>
+      </c>
+      <c r="B6023">
+        <v>861</v>
+      </c>
+      <c r="C6023">
+        <v>0</v>
+      </c>
+      <c r="D6023">
+        <v>0</v>
+      </c>
+      <c r="E6023">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6024">
+      <c r="A6024" s="2">
+        <v>46190</v>
+      </c>
+      <c r="B6024">
+        <v>861</v>
+      </c>
+      <c r="C6024">
+        <v>0</v>
+      </c>
+      <c r="D6024">
+        <v>0</v>
+      </c>
+      <c r="E6024">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6025">
+      <c r="A6025" s="2">
+        <v>46190</v>
+      </c>
+      <c r="B6025">
+        <v>861</v>
+      </c>
+      <c r="C6025">
+        <v>0</v>
+      </c>
+      <c r="D6025">
+        <v>0</v>
+      </c>
+      <c r="E6025">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6026">
+      <c r="A6026" s="2">
+        <v>46190</v>
+      </c>
+      <c r="B6026">
+        <v>861</v>
+      </c>
+      <c r="C6026">
+        <v>0</v>
+      </c>
+      <c r="D6026">
+        <v>0</v>
+      </c>
+      <c r="E6026">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6027">
+      <c r="A6027" s="2">
+        <v>46190</v>
+      </c>
+      <c r="B6027">
+        <v>861</v>
+      </c>
+      <c r="C6027">
+        <v>0</v>
+      </c>
+      <c r="D6027">
+        <v>0</v>
+      </c>
+      <c r="E6027">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6028">
+      <c r="A6028" s="2">
+        <v>46190</v>
+      </c>
+      <c r="B6028">
+        <v>861</v>
+      </c>
+      <c r="C6028">
+        <v>0</v>
+      </c>
+      <c r="D6028">
+        <v>0</v>
+      </c>
+      <c r="E6028">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data-raw/resultados_supersete.xlsx
+++ b/data-raw/resultados_supersete.xlsx
@@ -355,7 +355,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E6028"/>
+  <dimension ref="A1:E6035"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" style="2" customWidth="1"/>
@@ -102847,6 +102847,125 @@
         <v>0</v>
       </c>
     </row>
+    <row r="6029">
+      <c r="A6029" s="2">
+        <v>46193</v>
+      </c>
+      <c r="B6029">
+        <v>862</v>
+      </c>
+      <c r="C6029">
+        <v>0</v>
+      </c>
+      <c r="D6029">
+        <v>0</v>
+      </c>
+      <c r="E6029">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6030">
+      <c r="A6030" s="2">
+        <v>46193</v>
+      </c>
+      <c r="B6030">
+        <v>862</v>
+      </c>
+      <c r="C6030">
+        <v>0</v>
+      </c>
+      <c r="D6030">
+        <v>0</v>
+      </c>
+      <c r="E6030">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6031">
+      <c r="A6031" s="2">
+        <v>46193</v>
+      </c>
+      <c r="B6031">
+        <v>862</v>
+      </c>
+      <c r="C6031">
+        <v>0</v>
+      </c>
+      <c r="D6031">
+        <v>0</v>
+      </c>
+      <c r="E6031">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6032">
+      <c r="A6032" s="2">
+        <v>46193</v>
+      </c>
+      <c r="B6032">
+        <v>862</v>
+      </c>
+      <c r="C6032">
+        <v>0</v>
+      </c>
+      <c r="D6032">
+        <v>0</v>
+      </c>
+      <c r="E6032">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6033">
+      <c r="A6033" s="2">
+        <v>46193</v>
+      </c>
+      <c r="B6033">
+        <v>862</v>
+      </c>
+      <c r="C6033">
+        <v>0</v>
+      </c>
+      <c r="D6033">
+        <v>0</v>
+      </c>
+      <c r="E6033">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6034">
+      <c r="A6034" s="2">
+        <v>46193</v>
+      </c>
+      <c r="B6034">
+        <v>862</v>
+      </c>
+      <c r="C6034">
+        <v>0</v>
+      </c>
+      <c r="D6034">
+        <v>0</v>
+      </c>
+      <c r="E6034">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6035">
+      <c r="A6035" s="2">
+        <v>46193</v>
+      </c>
+      <c r="B6035">
+        <v>862</v>
+      </c>
+      <c r="C6035">
+        <v>0</v>
+      </c>
+      <c r="D6035">
+        <v>0</v>
+      </c>
+      <c r="E6035">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data-raw/resultados_supersete.xlsx
+++ b/data-raw/resultados_supersete.xlsx
@@ -355,7 +355,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E6035"/>
+  <dimension ref="A1:E6042"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" style="2" customWidth="1"/>
@@ -102966,6 +102966,125 @@
         <v>0</v>
       </c>
     </row>
+    <row r="6036">
+      <c r="A6036" s="2">
+        <v>46195</v>
+      </c>
+      <c r="B6036">
+        <v>863</v>
+      </c>
+      <c r="C6036">
+        <v>0</v>
+      </c>
+      <c r="D6036">
+        <v>0</v>
+      </c>
+      <c r="E6036">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6037">
+      <c r="A6037" s="2">
+        <v>46195</v>
+      </c>
+      <c r="B6037">
+        <v>863</v>
+      </c>
+      <c r="C6037">
+        <v>0</v>
+      </c>
+      <c r="D6037">
+        <v>0</v>
+      </c>
+      <c r="E6037">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6038">
+      <c r="A6038" s="2">
+        <v>46195</v>
+      </c>
+      <c r="B6038">
+        <v>863</v>
+      </c>
+      <c r="C6038">
+        <v>0</v>
+      </c>
+      <c r="D6038">
+        <v>0</v>
+      </c>
+      <c r="E6038">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6039">
+      <c r="A6039" s="2">
+        <v>46195</v>
+      </c>
+      <c r="B6039">
+        <v>863</v>
+      </c>
+      <c r="C6039">
+        <v>0</v>
+      </c>
+      <c r="D6039">
+        <v>0</v>
+      </c>
+      <c r="E6039">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6040">
+      <c r="A6040" s="2">
+        <v>46195</v>
+      </c>
+      <c r="B6040">
+        <v>863</v>
+      </c>
+      <c r="C6040">
+        <v>0</v>
+      </c>
+      <c r="D6040">
+        <v>0</v>
+      </c>
+      <c r="E6040">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6041">
+      <c r="A6041" s="2">
+        <v>46195</v>
+      </c>
+      <c r="B6041">
+        <v>863</v>
+      </c>
+      <c r="C6041">
+        <v>0</v>
+      </c>
+      <c r="D6041">
+        <v>0</v>
+      </c>
+      <c r="E6041">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6042">
+      <c r="A6042" s="2">
+        <v>46195</v>
+      </c>
+      <c r="B6042">
+        <v>863</v>
+      </c>
+      <c r="C6042">
+        <v>0</v>
+      </c>
+      <c r="D6042">
+        <v>0</v>
+      </c>
+      <c r="E6042">
+        <v>6</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data-raw/resultados_supersete.xlsx
+++ b/data-raw/resultados_supersete.xlsx
@@ -355,7 +355,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E6042"/>
+  <dimension ref="A1:E6049"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" style="2" customWidth="1"/>
@@ -103085,6 +103085,125 @@
         <v>6</v>
       </c>
     </row>
+    <row r="6043">
+      <c r="A6043" s="2">
+        <v>46198</v>
+      </c>
+      <c r="B6043">
+        <v>864</v>
+      </c>
+      <c r="C6043">
+        <v>0</v>
+      </c>
+      <c r="D6043">
+        <v>0</v>
+      </c>
+      <c r="E6043">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6044">
+      <c r="A6044" s="2">
+        <v>46198</v>
+      </c>
+      <c r="B6044">
+        <v>864</v>
+      </c>
+      <c r="C6044">
+        <v>0</v>
+      </c>
+      <c r="D6044">
+        <v>0</v>
+      </c>
+      <c r="E6044">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6045">
+      <c r="A6045" s="2">
+        <v>46198</v>
+      </c>
+      <c r="B6045">
+        <v>864</v>
+      </c>
+      <c r="C6045">
+        <v>0</v>
+      </c>
+      <c r="D6045">
+        <v>0</v>
+      </c>
+      <c r="E6045">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6046">
+      <c r="A6046" s="2">
+        <v>46198</v>
+      </c>
+      <c r="B6046">
+        <v>864</v>
+      </c>
+      <c r="C6046">
+        <v>0</v>
+      </c>
+      <c r="D6046">
+        <v>0</v>
+      </c>
+      <c r="E6046">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6047">
+      <c r="A6047" s="2">
+        <v>46198</v>
+      </c>
+      <c r="B6047">
+        <v>864</v>
+      </c>
+      <c r="C6047">
+        <v>0</v>
+      </c>
+      <c r="D6047">
+        <v>0</v>
+      </c>
+      <c r="E6047">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6048">
+      <c r="A6048" s="2">
+        <v>46198</v>
+      </c>
+      <c r="B6048">
+        <v>864</v>
+      </c>
+      <c r="C6048">
+        <v>0</v>
+      </c>
+      <c r="D6048">
+        <v>0</v>
+      </c>
+      <c r="E6048">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6049">
+      <c r="A6049" s="2">
+        <v>46198</v>
+      </c>
+      <c r="B6049">
+        <v>864</v>
+      </c>
+      <c r="C6049">
+        <v>0</v>
+      </c>
+      <c r="D6049">
+        <v>0</v>
+      </c>
+      <c r="E6049">
+        <v>3</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data-raw/resultados_supersete.xlsx
+++ b/data-raw/resultados_supersete.xlsx
@@ -355,7 +355,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E6049"/>
+  <dimension ref="A1:E6056"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" style="2" customWidth="1"/>
@@ -103204,6 +103204,125 @@
         <v>3</v>
       </c>
     </row>
+    <row r="6050">
+      <c r="A6050" s="2">
+        <v>46199</v>
+      </c>
+      <c r="B6050">
+        <v>865</v>
+      </c>
+      <c r="C6050">
+        <v>0</v>
+      </c>
+      <c r="D6050">
+        <v>0</v>
+      </c>
+      <c r="E6050">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6051">
+      <c r="A6051" s="2">
+        <v>46199</v>
+      </c>
+      <c r="B6051">
+        <v>865</v>
+      </c>
+      <c r="C6051">
+        <v>0</v>
+      </c>
+      <c r="D6051">
+        <v>0</v>
+      </c>
+      <c r="E6051">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6052">
+      <c r="A6052" s="2">
+        <v>46199</v>
+      </c>
+      <c r="B6052">
+        <v>865</v>
+      </c>
+      <c r="C6052">
+        <v>0</v>
+      </c>
+      <c r="D6052">
+        <v>0</v>
+      </c>
+      <c r="E6052">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6053">
+      <c r="A6053" s="2">
+        <v>46199</v>
+      </c>
+      <c r="B6053">
+        <v>865</v>
+      </c>
+      <c r="C6053">
+        <v>0</v>
+      </c>
+      <c r="D6053">
+        <v>0</v>
+      </c>
+      <c r="E6053">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6054">
+      <c r="A6054" s="2">
+        <v>46199</v>
+      </c>
+      <c r="B6054">
+        <v>865</v>
+      </c>
+      <c r="C6054">
+        <v>0</v>
+      </c>
+      <c r="D6054">
+        <v>0</v>
+      </c>
+      <c r="E6054">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6055">
+      <c r="A6055" s="2">
+        <v>46199</v>
+      </c>
+      <c r="B6055">
+        <v>865</v>
+      </c>
+      <c r="C6055">
+        <v>0</v>
+      </c>
+      <c r="D6055">
+        <v>0</v>
+      </c>
+      <c r="E6055">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6056">
+      <c r="A6056" s="2">
+        <v>46199</v>
+      </c>
+      <c r="B6056">
+        <v>865</v>
+      </c>
+      <c r="C6056">
+        <v>0</v>
+      </c>
+      <c r="D6056">
+        <v>0</v>
+      </c>
+      <c r="E6056">
+        <v>2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data-raw/resultados_supersete.xlsx
+++ b/data-raw/resultados_supersete.xlsx
@@ -355,7 +355,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E6056"/>
+  <dimension ref="A1:E6063"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" style="2" customWidth="1"/>
@@ -103323,6 +103323,125 @@
         <v>2</v>
       </c>
     </row>
+    <row r="6057">
+      <c r="A6057" s="2">
+        <v>46202</v>
+      </c>
+      <c r="B6057">
+        <v>866</v>
+      </c>
+      <c r="C6057">
+        <v>0</v>
+      </c>
+      <c r="D6057">
+        <v>0</v>
+      </c>
+      <c r="E6057">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6058">
+      <c r="A6058" s="2">
+        <v>46202</v>
+      </c>
+      <c r="B6058">
+        <v>866</v>
+      </c>
+      <c r="C6058">
+        <v>0</v>
+      </c>
+      <c r="D6058">
+        <v>0</v>
+      </c>
+      <c r="E6058">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6059">
+      <c r="A6059" s="2">
+        <v>46202</v>
+      </c>
+      <c r="B6059">
+        <v>866</v>
+      </c>
+      <c r="C6059">
+        <v>0</v>
+      </c>
+      <c r="D6059">
+        <v>0</v>
+      </c>
+      <c r="E6059">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6060">
+      <c r="A6060" s="2">
+        <v>46202</v>
+      </c>
+      <c r="B6060">
+        <v>866</v>
+      </c>
+      <c r="C6060">
+        <v>0</v>
+      </c>
+      <c r="D6060">
+        <v>0</v>
+      </c>
+      <c r="E6060">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6061">
+      <c r="A6061" s="2">
+        <v>46202</v>
+      </c>
+      <c r="B6061">
+        <v>866</v>
+      </c>
+      <c r="C6061">
+        <v>0</v>
+      </c>
+      <c r="D6061">
+        <v>0</v>
+      </c>
+      <c r="E6061">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6062">
+      <c r="A6062" s="2">
+        <v>46202</v>
+      </c>
+      <c r="B6062">
+        <v>866</v>
+      </c>
+      <c r="C6062">
+        <v>0</v>
+      </c>
+      <c r="D6062">
+        <v>0</v>
+      </c>
+      <c r="E6062">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6063">
+      <c r="A6063" s="2">
+        <v>46202</v>
+      </c>
+      <c r="B6063">
+        <v>866</v>
+      </c>
+      <c r="C6063">
+        <v>0</v>
+      </c>
+      <c r="D6063">
+        <v>0</v>
+      </c>
+      <c r="E6063">
+        <v>5</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data-raw/resultados_supersete.xlsx
+++ b/data-raw/resultados_supersete.xlsx
@@ -355,7 +355,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E6063"/>
+  <dimension ref="A1:E6070"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" style="2" customWidth="1"/>
@@ -103442,6 +103442,125 @@
         <v>5</v>
       </c>
     </row>
+    <row r="6064">
+      <c r="A6064" s="2">
+        <v>46204</v>
+      </c>
+      <c r="B6064">
+        <v>867</v>
+      </c>
+      <c r="C6064">
+        <v>0</v>
+      </c>
+      <c r="D6064">
+        <v>0</v>
+      </c>
+      <c r="E6064">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6065">
+      <c r="A6065" s="2">
+        <v>46204</v>
+      </c>
+      <c r="B6065">
+        <v>867</v>
+      </c>
+      <c r="C6065">
+        <v>0</v>
+      </c>
+      <c r="D6065">
+        <v>0</v>
+      </c>
+      <c r="E6065">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6066">
+      <c r="A6066" s="2">
+        <v>46204</v>
+      </c>
+      <c r="B6066">
+        <v>867</v>
+      </c>
+      <c r="C6066">
+        <v>0</v>
+      </c>
+      <c r="D6066">
+        <v>0</v>
+      </c>
+      <c r="E6066">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6067">
+      <c r="A6067" s="2">
+        <v>46204</v>
+      </c>
+      <c r="B6067">
+        <v>867</v>
+      </c>
+      <c r="C6067">
+        <v>0</v>
+      </c>
+      <c r="D6067">
+        <v>0</v>
+      </c>
+      <c r="E6067">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6068">
+      <c r="A6068" s="2">
+        <v>46204</v>
+      </c>
+      <c r="B6068">
+        <v>867</v>
+      </c>
+      <c r="C6068">
+        <v>0</v>
+      </c>
+      <c r="D6068">
+        <v>0</v>
+      </c>
+      <c r="E6068">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6069">
+      <c r="A6069" s="2">
+        <v>46204</v>
+      </c>
+      <c r="B6069">
+        <v>867</v>
+      </c>
+      <c r="C6069">
+        <v>0</v>
+      </c>
+      <c r="D6069">
+        <v>0</v>
+      </c>
+      <c r="E6069">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6070">
+      <c r="A6070" s="2">
+        <v>46204</v>
+      </c>
+      <c r="B6070">
+        <v>867</v>
+      </c>
+      <c r="C6070">
+        <v>0</v>
+      </c>
+      <c r="D6070">
+        <v>0</v>
+      </c>
+      <c r="E6070">
+        <v>5</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data-raw/resultados_supersete.xlsx
+++ b/data-raw/resultados_supersete.xlsx
@@ -355,7 +355,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E6070"/>
+  <dimension ref="A1:E6077"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" style="2" customWidth="1"/>
@@ -103561,6 +103561,125 @@
         <v>5</v>
       </c>
     </row>
+    <row r="6071">
+      <c r="A6071" s="2">
+        <v>46206</v>
+      </c>
+      <c r="B6071">
+        <v>868</v>
+      </c>
+      <c r="C6071">
+        <v>0</v>
+      </c>
+      <c r="D6071">
+        <v>0</v>
+      </c>
+      <c r="E6071">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6072">
+      <c r="A6072" s="2">
+        <v>46206</v>
+      </c>
+      <c r="B6072">
+        <v>868</v>
+      </c>
+      <c r="C6072">
+        <v>0</v>
+      </c>
+      <c r="D6072">
+        <v>0</v>
+      </c>
+      <c r="E6072">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6073">
+      <c r="A6073" s="2">
+        <v>46206</v>
+      </c>
+      <c r="B6073">
+        <v>868</v>
+      </c>
+      <c r="C6073">
+        <v>0</v>
+      </c>
+      <c r="D6073">
+        <v>0</v>
+      </c>
+      <c r="E6073">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6074">
+      <c r="A6074" s="2">
+        <v>46206</v>
+      </c>
+      <c r="B6074">
+        <v>868</v>
+      </c>
+      <c r="C6074">
+        <v>0</v>
+      </c>
+      <c r="D6074">
+        <v>0</v>
+      </c>
+      <c r="E6074">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6075">
+      <c r="A6075" s="2">
+        <v>46206</v>
+      </c>
+      <c r="B6075">
+        <v>868</v>
+      </c>
+      <c r="C6075">
+        <v>0</v>
+      </c>
+      <c r="D6075">
+        <v>0</v>
+      </c>
+      <c r="E6075">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6076">
+      <c r="A6076" s="2">
+        <v>46206</v>
+      </c>
+      <c r="B6076">
+        <v>868</v>
+      </c>
+      <c r="C6076">
+        <v>0</v>
+      </c>
+      <c r="D6076">
+        <v>0</v>
+      </c>
+      <c r="E6076">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6077">
+      <c r="A6077" s="2">
+        <v>46206</v>
+      </c>
+      <c r="B6077">
+        <v>868</v>
+      </c>
+      <c r="C6077">
+        <v>0</v>
+      </c>
+      <c r="D6077">
+        <v>0</v>
+      </c>
+      <c r="E6077">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data-raw/resultados_supersete.xlsx
+++ b/data-raw/resultados_supersete.xlsx
@@ -355,7 +355,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E6077"/>
+  <dimension ref="A1:E6084"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" style="2" customWidth="1"/>
@@ -103680,6 +103680,125 @@
         <v>9</v>
       </c>
     </row>
+    <row r="6078">
+      <c r="A6078" s="2">
+        <v>46209</v>
+      </c>
+      <c r="B6078">
+        <v>869</v>
+      </c>
+      <c r="C6078">
+        <v>0</v>
+      </c>
+      <c r="D6078">
+        <v>0</v>
+      </c>
+      <c r="E6078">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6079">
+      <c r="A6079" s="2">
+        <v>46209</v>
+      </c>
+      <c r="B6079">
+        <v>869</v>
+      </c>
+      <c r="C6079">
+        <v>0</v>
+      </c>
+      <c r="D6079">
+        <v>0</v>
+      </c>
+      <c r="E6079">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6080">
+      <c r="A6080" s="2">
+        <v>46209</v>
+      </c>
+      <c r="B6080">
+        <v>869</v>
+      </c>
+      <c r="C6080">
+        <v>0</v>
+      </c>
+      <c r="D6080">
+        <v>0</v>
+      </c>
+      <c r="E6080">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6081">
+      <c r="A6081" s="2">
+        <v>46209</v>
+      </c>
+      <c r="B6081">
+        <v>869</v>
+      </c>
+      <c r="C6081">
+        <v>0</v>
+      </c>
+      <c r="D6081">
+        <v>0</v>
+      </c>
+      <c r="E6081">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6082">
+      <c r="A6082" s="2">
+        <v>46209</v>
+      </c>
+      <c r="B6082">
+        <v>869</v>
+      </c>
+      <c r="C6082">
+        <v>0</v>
+      </c>
+      <c r="D6082">
+        <v>0</v>
+      </c>
+      <c r="E6082">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6083">
+      <c r="A6083" s="2">
+        <v>46209</v>
+      </c>
+      <c r="B6083">
+        <v>869</v>
+      </c>
+      <c r="C6083">
+        <v>0</v>
+      </c>
+      <c r="D6083">
+        <v>0</v>
+      </c>
+      <c r="E6083">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6084">
+      <c r="A6084" s="2">
+        <v>46209</v>
+      </c>
+      <c r="B6084">
+        <v>869</v>
+      </c>
+      <c r="C6084">
+        <v>0</v>
+      </c>
+      <c r="D6084">
+        <v>0</v>
+      </c>
+      <c r="E6084">
+        <v>6</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data-raw/resultados_supersete.xlsx
+++ b/data-raw/resultados_supersete.xlsx
@@ -355,7 +355,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E6084"/>
+  <dimension ref="A1:E6091"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" style="2" customWidth="1"/>
@@ -103799,6 +103799,125 @@
         <v>6</v>
       </c>
     </row>
+    <row r="6085">
+      <c r="A6085" s="2">
+        <v>46211</v>
+      </c>
+      <c r="B6085">
+        <v>870</v>
+      </c>
+      <c r="C6085">
+        <v>0</v>
+      </c>
+      <c r="D6085">
+        <v>0</v>
+      </c>
+      <c r="E6085">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6086">
+      <c r="A6086" s="2">
+        <v>46211</v>
+      </c>
+      <c r="B6086">
+        <v>870</v>
+      </c>
+      <c r="C6086">
+        <v>0</v>
+      </c>
+      <c r="D6086">
+        <v>0</v>
+      </c>
+      <c r="E6086">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6087">
+      <c r="A6087" s="2">
+        <v>46211</v>
+      </c>
+      <c r="B6087">
+        <v>870</v>
+      </c>
+      <c r="C6087">
+        <v>0</v>
+      </c>
+      <c r="D6087">
+        <v>0</v>
+      </c>
+      <c r="E6087">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6088">
+      <c r="A6088" s="2">
+        <v>46211</v>
+      </c>
+      <c r="B6088">
+        <v>870</v>
+      </c>
+      <c r="C6088">
+        <v>0</v>
+      </c>
+      <c r="D6088">
+        <v>0</v>
+      </c>
+      <c r="E6088">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6089">
+      <c r="A6089" s="2">
+        <v>46211</v>
+      </c>
+      <c r="B6089">
+        <v>870</v>
+      </c>
+      <c r="C6089">
+        <v>0</v>
+      </c>
+      <c r="D6089">
+        <v>0</v>
+      </c>
+      <c r="E6089">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6090">
+      <c r="A6090" s="2">
+        <v>46211</v>
+      </c>
+      <c r="B6090">
+        <v>870</v>
+      </c>
+      <c r="C6090">
+        <v>0</v>
+      </c>
+      <c r="D6090">
+        <v>0</v>
+      </c>
+      <c r="E6090">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6091">
+      <c r="A6091" s="2">
+        <v>46211</v>
+      </c>
+      <c r="B6091">
+        <v>870</v>
+      </c>
+      <c r="C6091">
+        <v>0</v>
+      </c>
+      <c r="D6091">
+        <v>0</v>
+      </c>
+      <c r="E6091">
+        <v>2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data-raw/resultados_supersete.xlsx
+++ b/data-raw/resultados_supersete.xlsx
@@ -355,7 +355,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E6091"/>
+  <dimension ref="A1:E6098"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" style="2" customWidth="1"/>
@@ -103918,6 +103918,125 @@
         <v>2</v>
       </c>
     </row>
+    <row r="6092">
+      <c r="A6092" s="2">
+        <v>46213</v>
+      </c>
+      <c r="B6092">
+        <v>871</v>
+      </c>
+      <c r="C6092">
+        <v>0</v>
+      </c>
+      <c r="D6092">
+        <v>0</v>
+      </c>
+      <c r="E6092">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6093">
+      <c r="A6093" s="2">
+        <v>46213</v>
+      </c>
+      <c r="B6093">
+        <v>871</v>
+      </c>
+      <c r="C6093">
+        <v>0</v>
+      </c>
+      <c r="D6093">
+        <v>0</v>
+      </c>
+      <c r="E6093">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6094">
+      <c r="A6094" s="2">
+        <v>46213</v>
+      </c>
+      <c r="B6094">
+        <v>871</v>
+      </c>
+      <c r="C6094">
+        <v>0</v>
+      </c>
+      <c r="D6094">
+        <v>0</v>
+      </c>
+      <c r="E6094">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6095">
+      <c r="A6095" s="2">
+        <v>46213</v>
+      </c>
+      <c r="B6095">
+        <v>871</v>
+      </c>
+      <c r="C6095">
+        <v>0</v>
+      </c>
+      <c r="D6095">
+        <v>0</v>
+      </c>
+      <c r="E6095">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6096">
+      <c r="A6096" s="2">
+        <v>46213</v>
+      </c>
+      <c r="B6096">
+        <v>871</v>
+      </c>
+      <c r="C6096">
+        <v>0</v>
+      </c>
+      <c r="D6096">
+        <v>0</v>
+      </c>
+      <c r="E6096">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6097">
+      <c r="A6097" s="2">
+        <v>46213</v>
+      </c>
+      <c r="B6097">
+        <v>871</v>
+      </c>
+      <c r="C6097">
+        <v>0</v>
+      </c>
+      <c r="D6097">
+        <v>0</v>
+      </c>
+      <c r="E6097">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6098">
+      <c r="A6098" s="2">
+        <v>46213</v>
+      </c>
+      <c r="B6098">
+        <v>871</v>
+      </c>
+      <c r="C6098">
+        <v>0</v>
+      </c>
+      <c r="D6098">
+        <v>0</v>
+      </c>
+      <c r="E6098">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data-raw/resultados_supersete.xlsx
+++ b/data-raw/resultados_supersete.xlsx
@@ -355,7 +355,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E6098"/>
+  <dimension ref="A1:E6105"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" style="2" customWidth="1"/>
@@ -104037,6 +104037,125 @@
         <v>7</v>
       </c>
     </row>
+    <row r="6099">
+      <c r="A6099" s="2">
+        <v>46216</v>
+      </c>
+      <c r="B6099">
+        <v>872</v>
+      </c>
+      <c r="C6099">
+        <v>0</v>
+      </c>
+      <c r="D6099">
+        <v>0</v>
+      </c>
+      <c r="E6099">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6100">
+      <c r="A6100" s="2">
+        <v>46216</v>
+      </c>
+      <c r="B6100">
+        <v>872</v>
+      </c>
+      <c r="C6100">
+        <v>0</v>
+      </c>
+      <c r="D6100">
+        <v>0</v>
+      </c>
+      <c r="E6100">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6101">
+      <c r="A6101" s="2">
+        <v>46216</v>
+      </c>
+      <c r="B6101">
+        <v>872</v>
+      </c>
+      <c r="C6101">
+        <v>0</v>
+      </c>
+      <c r="D6101">
+        <v>0</v>
+      </c>
+      <c r="E6101">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6102">
+      <c r="A6102" s="2">
+        <v>46216</v>
+      </c>
+      <c r="B6102">
+        <v>872</v>
+      </c>
+      <c r="C6102">
+        <v>0</v>
+      </c>
+      <c r="D6102">
+        <v>0</v>
+      </c>
+      <c r="E6102">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6103">
+      <c r="A6103" s="2">
+        <v>46216</v>
+      </c>
+      <c r="B6103">
+        <v>872</v>
+      </c>
+      <c r="C6103">
+        <v>0</v>
+      </c>
+      <c r="D6103">
+        <v>0</v>
+      </c>
+      <c r="E6103">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6104">
+      <c r="A6104" s="2">
+        <v>46216</v>
+      </c>
+      <c r="B6104">
+        <v>872</v>
+      </c>
+      <c r="C6104">
+        <v>0</v>
+      </c>
+      <c r="D6104">
+        <v>0</v>
+      </c>
+      <c r="E6104">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6105">
+      <c r="A6105" s="2">
+        <v>46216</v>
+      </c>
+      <c r="B6105">
+        <v>872</v>
+      </c>
+      <c r="C6105">
+        <v>0</v>
+      </c>
+      <c r="D6105">
+        <v>0</v>
+      </c>
+      <c r="E6105">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data-raw/resultados_supersete.xlsx
+++ b/data-raw/resultados_supersete.xlsx
@@ -355,7 +355,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E6105"/>
+  <dimension ref="A1:E6112"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" style="2" customWidth="1"/>
@@ -104156,6 +104156,125 @@
         <v>1</v>
       </c>
     </row>
+    <row r="6106">
+      <c r="A6106" s="2">
+        <v>46218</v>
+      </c>
+      <c r="B6106">
+        <v>873</v>
+      </c>
+      <c r="C6106">
+        <v>0</v>
+      </c>
+      <c r="D6106">
+        <v>0</v>
+      </c>
+      <c r="E6106">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6107">
+      <c r="A6107" s="2">
+        <v>46218</v>
+      </c>
+      <c r="B6107">
+        <v>873</v>
+      </c>
+      <c r="C6107">
+        <v>0</v>
+      </c>
+      <c r="D6107">
+        <v>0</v>
+      </c>
+      <c r="E6107">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6108">
+      <c r="A6108" s="2">
+        <v>46218</v>
+      </c>
+      <c r="B6108">
+        <v>873</v>
+      </c>
+      <c r="C6108">
+        <v>0</v>
+      </c>
+      <c r="D6108">
+        <v>0</v>
+      </c>
+      <c r="E6108">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6109">
+      <c r="A6109" s="2">
+        <v>46218</v>
+      </c>
+      <c r="B6109">
+        <v>873</v>
+      </c>
+      <c r="C6109">
+        <v>0</v>
+      </c>
+      <c r="D6109">
+        <v>0</v>
+      </c>
+      <c r="E6109">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6110">
+      <c r="A6110" s="2">
+        <v>46218</v>
+      </c>
+      <c r="B6110">
+        <v>873</v>
+      </c>
+      <c r="C6110">
+        <v>0</v>
+      </c>
+      <c r="D6110">
+        <v>0</v>
+      </c>
+      <c r="E6110">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6111">
+      <c r="A6111" s="2">
+        <v>46218</v>
+      </c>
+      <c r="B6111">
+        <v>873</v>
+      </c>
+      <c r="C6111">
+        <v>0</v>
+      </c>
+      <c r="D6111">
+        <v>0</v>
+      </c>
+      <c r="E6111">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6112">
+      <c r="A6112" s="2">
+        <v>46218</v>
+      </c>
+      <c r="B6112">
+        <v>873</v>
+      </c>
+      <c r="C6112">
+        <v>0</v>
+      </c>
+      <c r="D6112">
+        <v>0</v>
+      </c>
+      <c r="E6112">
+        <v>2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data-raw/resultados_supersete.xlsx
+++ b/data-raw/resultados_supersete.xlsx
@@ -355,7 +355,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E6112"/>
+  <dimension ref="A1:E6119"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" style="2" customWidth="1"/>
@@ -104275,6 +104275,125 @@
         <v>2</v>
       </c>
     </row>
+    <row r="6113">
+      <c r="A6113" s="2">
+        <v>46220</v>
+      </c>
+      <c r="B6113">
+        <v>874</v>
+      </c>
+      <c r="C6113">
+        <v>0</v>
+      </c>
+      <c r="D6113">
+        <v>0</v>
+      </c>
+      <c r="E6113">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6114">
+      <c r="A6114" s="2">
+        <v>46220</v>
+      </c>
+      <c r="B6114">
+        <v>874</v>
+      </c>
+      <c r="C6114">
+        <v>0</v>
+      </c>
+      <c r="D6114">
+        <v>0</v>
+      </c>
+      <c r="E6114">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6115">
+      <c r="A6115" s="2">
+        <v>46220</v>
+      </c>
+      <c r="B6115">
+        <v>874</v>
+      </c>
+      <c r="C6115">
+        <v>0</v>
+      </c>
+      <c r="D6115">
+        <v>0</v>
+      </c>
+      <c r="E6115">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6116">
+      <c r="A6116" s="2">
+        <v>46220</v>
+      </c>
+      <c r="B6116">
+        <v>874</v>
+      </c>
+      <c r="C6116">
+        <v>0</v>
+      </c>
+      <c r="D6116">
+        <v>0</v>
+      </c>
+      <c r="E6116">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6117">
+      <c r="A6117" s="2">
+        <v>46220</v>
+      </c>
+      <c r="B6117">
+        <v>874</v>
+      </c>
+      <c r="C6117">
+        <v>0</v>
+      </c>
+      <c r="D6117">
+        <v>0</v>
+      </c>
+      <c r="E6117">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6118">
+      <c r="A6118" s="2">
+        <v>46220</v>
+      </c>
+      <c r="B6118">
+        <v>874</v>
+      </c>
+      <c r="C6118">
+        <v>0</v>
+      </c>
+      <c r="D6118">
+        <v>0</v>
+      </c>
+      <c r="E6118">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6119">
+      <c r="A6119" s="2">
+        <v>46220</v>
+      </c>
+      <c r="B6119">
+        <v>874</v>
+      </c>
+      <c r="C6119">
+        <v>0</v>
+      </c>
+      <c r="D6119">
+        <v>0</v>
+      </c>
+      <c r="E6119">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data-raw/resultados_supersete.xlsx
+++ b/data-raw/resultados_supersete.xlsx
@@ -355,7 +355,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E6119"/>
+  <dimension ref="A1:E6126"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" style="2" customWidth="1"/>
@@ -104394,6 +104394,125 @@
         <v>8</v>
       </c>
     </row>
+    <row r="6120">
+      <c r="A6120" s="2">
+        <v>46223</v>
+      </c>
+      <c r="B6120">
+        <v>875</v>
+      </c>
+      <c r="C6120">
+        <v>0</v>
+      </c>
+      <c r="D6120">
+        <v>0</v>
+      </c>
+      <c r="E6120">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6121">
+      <c r="A6121" s="2">
+        <v>46223</v>
+      </c>
+      <c r="B6121">
+        <v>875</v>
+      </c>
+      <c r="C6121">
+        <v>0</v>
+      </c>
+      <c r="D6121">
+        <v>0</v>
+      </c>
+      <c r="E6121">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6122">
+      <c r="A6122" s="2">
+        <v>46223</v>
+      </c>
+      <c r="B6122">
+        <v>875</v>
+      </c>
+      <c r="C6122">
+        <v>0</v>
+      </c>
+      <c r="D6122">
+        <v>0</v>
+      </c>
+      <c r="E6122">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6123">
+      <c r="A6123" s="2">
+        <v>46223</v>
+      </c>
+      <c r="B6123">
+        <v>875</v>
+      </c>
+      <c r="C6123">
+        <v>0</v>
+      </c>
+      <c r="D6123">
+        <v>0</v>
+      </c>
+      <c r="E6123">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6124">
+      <c r="A6124" s="2">
+        <v>46223</v>
+      </c>
+      <c r="B6124">
+        <v>875</v>
+      </c>
+      <c r="C6124">
+        <v>0</v>
+      </c>
+      <c r="D6124">
+        <v>0</v>
+      </c>
+      <c r="E6124">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6125">
+      <c r="A6125" s="2">
+        <v>46223</v>
+      </c>
+      <c r="B6125">
+        <v>875</v>
+      </c>
+      <c r="C6125">
+        <v>0</v>
+      </c>
+      <c r="D6125">
+        <v>0</v>
+      </c>
+      <c r="E6125">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6126">
+      <c r="A6126" s="2">
+        <v>46223</v>
+      </c>
+      <c r="B6126">
+        <v>875</v>
+      </c>
+      <c r="C6126">
+        <v>0</v>
+      </c>
+      <c r="D6126">
+        <v>0</v>
+      </c>
+      <c r="E6126">
+        <v>6</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data-raw/resultados_supersete.xlsx
+++ b/data-raw/resultados_supersete.xlsx
@@ -355,7 +355,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E6126"/>
+  <dimension ref="A1:E6133"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" style="2" customWidth="1"/>
@@ -104513,6 +104513,125 @@
         <v>6</v>
       </c>
     </row>
+    <row r="6127">
+      <c r="A6127" s="2">
+        <v>46225</v>
+      </c>
+      <c r="B6127">
+        <v>876</v>
+      </c>
+      <c r="C6127">
+        <v>0</v>
+      </c>
+      <c r="D6127">
+        <v>0</v>
+      </c>
+      <c r="E6127">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6128">
+      <c r="A6128" s="2">
+        <v>46225</v>
+      </c>
+      <c r="B6128">
+        <v>876</v>
+      </c>
+      <c r="C6128">
+        <v>0</v>
+      </c>
+      <c r="D6128">
+        <v>0</v>
+      </c>
+      <c r="E6128">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6129">
+      <c r="A6129" s="2">
+        <v>46225</v>
+      </c>
+      <c r="B6129">
+        <v>876</v>
+      </c>
+      <c r="C6129">
+        <v>0</v>
+      </c>
+      <c r="D6129">
+        <v>0</v>
+      </c>
+      <c r="E6129">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6130">
+      <c r="A6130" s="2">
+        <v>46225</v>
+      </c>
+      <c r="B6130">
+        <v>876</v>
+      </c>
+      <c r="C6130">
+        <v>0</v>
+      </c>
+      <c r="D6130">
+        <v>0</v>
+      </c>
+      <c r="E6130">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6131">
+      <c r="A6131" s="2">
+        <v>46225</v>
+      </c>
+      <c r="B6131">
+        <v>876</v>
+      </c>
+      <c r="C6131">
+        <v>0</v>
+      </c>
+      <c r="D6131">
+        <v>0</v>
+      </c>
+      <c r="E6131">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6132">
+      <c r="A6132" s="2">
+        <v>46225</v>
+      </c>
+      <c r="B6132">
+        <v>876</v>
+      </c>
+      <c r="C6132">
+        <v>0</v>
+      </c>
+      <c r="D6132">
+        <v>0</v>
+      </c>
+      <c r="E6132">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6133">
+      <c r="A6133" s="2">
+        <v>46225</v>
+      </c>
+      <c r="B6133">
+        <v>876</v>
+      </c>
+      <c r="C6133">
+        <v>0</v>
+      </c>
+      <c r="D6133">
+        <v>0</v>
+      </c>
+      <c r="E6133">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data-raw/resultados_supersete.xlsx
+++ b/data-raw/resultados_supersete.xlsx
@@ -355,7 +355,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E6133"/>
+  <dimension ref="A1:E6140"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" style="2" customWidth="1"/>
@@ -104632,6 +104632,125 @@
         <v>7</v>
       </c>
     </row>
+    <row r="6134">
+      <c r="A6134" s="2">
+        <v>46227</v>
+      </c>
+      <c r="B6134">
+        <v>877</v>
+      </c>
+      <c r="C6134">
+        <v>0</v>
+      </c>
+      <c r="D6134">
+        <v>0</v>
+      </c>
+      <c r="E6134">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6135">
+      <c r="A6135" s="2">
+        <v>46227</v>
+      </c>
+      <c r="B6135">
+        <v>877</v>
+      </c>
+      <c r="C6135">
+        <v>0</v>
+      </c>
+      <c r="D6135">
+        <v>0</v>
+      </c>
+      <c r="E6135">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6136">
+      <c r="A6136" s="2">
+        <v>46227</v>
+      </c>
+      <c r="B6136">
+        <v>877</v>
+      </c>
+      <c r="C6136">
+        <v>0</v>
+      </c>
+      <c r="D6136">
+        <v>0</v>
+      </c>
+      <c r="E6136">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6137">
+      <c r="A6137" s="2">
+        <v>46227</v>
+      </c>
+      <c r="B6137">
+        <v>877</v>
+      </c>
+      <c r="C6137">
+        <v>0</v>
+      </c>
+      <c r="D6137">
+        <v>0</v>
+      </c>
+      <c r="E6137">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6138">
+      <c r="A6138" s="2">
+        <v>46227</v>
+      </c>
+      <c r="B6138">
+        <v>877</v>
+      </c>
+      <c r="C6138">
+        <v>0</v>
+      </c>
+      <c r="D6138">
+        <v>0</v>
+      </c>
+      <c r="E6138">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6139">
+      <c r="A6139" s="2">
+        <v>46227</v>
+      </c>
+      <c r="B6139">
+        <v>877</v>
+      </c>
+      <c r="C6139">
+        <v>0</v>
+      </c>
+      <c r="D6139">
+        <v>0</v>
+      </c>
+      <c r="E6139">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6140">
+      <c r="A6140" s="2">
+        <v>46227</v>
+      </c>
+      <c r="B6140">
+        <v>877</v>
+      </c>
+      <c r="C6140">
+        <v>0</v>
+      </c>
+      <c r="D6140">
+        <v>0</v>
+      </c>
+      <c r="E6140">
+        <v>3</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data-raw/resultados_supersete.xlsx
+++ b/data-raw/resultados_supersete.xlsx
@@ -355,7 +355,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E6140"/>
+  <dimension ref="A1:E6147"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" style="2" customWidth="1"/>
@@ -104751,6 +104751,125 @@
         <v>3</v>
       </c>
     </row>
+    <row r="6141">
+      <c r="A6141" s="2">
+        <v>46230</v>
+      </c>
+      <c r="B6141">
+        <v>878</v>
+      </c>
+      <c r="C6141">
+        <v>0</v>
+      </c>
+      <c r="D6141">
+        <v>0</v>
+      </c>
+      <c r="E6141">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6142">
+      <c r="A6142" s="2">
+        <v>46230</v>
+      </c>
+      <c r="B6142">
+        <v>878</v>
+      </c>
+      <c r="C6142">
+        <v>0</v>
+      </c>
+      <c r="D6142">
+        <v>0</v>
+      </c>
+      <c r="E6142">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6143">
+      <c r="A6143" s="2">
+        <v>46230</v>
+      </c>
+      <c r="B6143">
+        <v>878</v>
+      </c>
+      <c r="C6143">
+        <v>0</v>
+      </c>
+      <c r="D6143">
+        <v>0</v>
+      </c>
+      <c r="E6143">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6144">
+      <c r="A6144" s="2">
+        <v>46230</v>
+      </c>
+      <c r="B6144">
+        <v>878</v>
+      </c>
+      <c r="C6144">
+        <v>0</v>
+      </c>
+      <c r="D6144">
+        <v>0</v>
+      </c>
+      <c r="E6144">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6145">
+      <c r="A6145" s="2">
+        <v>46230</v>
+      </c>
+      <c r="B6145">
+        <v>878</v>
+      </c>
+      <c r="C6145">
+        <v>0</v>
+      </c>
+      <c r="D6145">
+        <v>0</v>
+      </c>
+      <c r="E6145">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6146">
+      <c r="A6146" s="2">
+        <v>46230</v>
+      </c>
+      <c r="B6146">
+        <v>878</v>
+      </c>
+      <c r="C6146">
+        <v>0</v>
+      </c>
+      <c r="D6146">
+        <v>0</v>
+      </c>
+      <c r="E6146">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6147">
+      <c r="A6147" s="2">
+        <v>46230</v>
+      </c>
+      <c r="B6147">
+        <v>878</v>
+      </c>
+      <c r="C6147">
+        <v>0</v>
+      </c>
+      <c r="D6147">
+        <v>0</v>
+      </c>
+      <c r="E6147">
+        <v>3</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data-raw/resultados_supersete.xlsx
+++ b/data-raw/resultados_supersete.xlsx
@@ -355,7 +355,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E6147"/>
+  <dimension ref="A1:E6154"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" style="2" customWidth="1"/>
@@ -104870,6 +104870,125 @@
         <v>3</v>
       </c>
     </row>
+    <row r="6148">
+      <c r="A6148" s="2">
+        <v>46232</v>
+      </c>
+      <c r="B6148">
+        <v>879</v>
+      </c>
+      <c r="C6148">
+        <v>0</v>
+      </c>
+      <c r="D6148">
+        <v>0</v>
+      </c>
+      <c r="E6148">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6149">
+      <c r="A6149" s="2">
+        <v>46232</v>
+      </c>
+      <c r="B6149">
+        <v>879</v>
+      </c>
+      <c r="C6149">
+        <v>0</v>
+      </c>
+      <c r="D6149">
+        <v>0</v>
+      </c>
+      <c r="E6149">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6150">
+      <c r="A6150" s="2">
+        <v>46232</v>
+      </c>
+      <c r="B6150">
+        <v>879</v>
+      </c>
+      <c r="C6150">
+        <v>0</v>
+      </c>
+      <c r="D6150">
+        <v>0</v>
+      </c>
+      <c r="E6150">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6151">
+      <c r="A6151" s="2">
+        <v>46232</v>
+      </c>
+      <c r="B6151">
+        <v>879</v>
+      </c>
+      <c r="C6151">
+        <v>0</v>
+      </c>
+      <c r="D6151">
+        <v>0</v>
+      </c>
+      <c r="E6151">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6152">
+      <c r="A6152" s="2">
+        <v>46232</v>
+      </c>
+      <c r="B6152">
+        <v>879</v>
+      </c>
+      <c r="C6152">
+        <v>0</v>
+      </c>
+      <c r="D6152">
+        <v>0</v>
+      </c>
+      <c r="E6152">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6153">
+      <c r="A6153" s="2">
+        <v>46232</v>
+      </c>
+      <c r="B6153">
+        <v>879</v>
+      </c>
+      <c r="C6153">
+        <v>0</v>
+      </c>
+      <c r="D6153">
+        <v>0</v>
+      </c>
+      <c r="E6153">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6154">
+      <c r="A6154" s="2">
+        <v>46232</v>
+      </c>
+      <c r="B6154">
+        <v>879</v>
+      </c>
+      <c r="C6154">
+        <v>0</v>
+      </c>
+      <c r="D6154">
+        <v>0</v>
+      </c>
+      <c r="E6154">
+        <v>2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data-raw/resultados_supersete.xlsx
+++ b/data-raw/resultados_supersete.xlsx
@@ -355,7 +355,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E6154"/>
+  <dimension ref="A1:E6161"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" style="2" customWidth="1"/>
@@ -104989,6 +104989,125 @@
         <v>2</v>
       </c>
     </row>
+    <row r="6155">
+      <c r="A6155" s="2">
+        <v>46234</v>
+      </c>
+      <c r="B6155">
+        <v>880</v>
+      </c>
+      <c r="C6155">
+        <v>0</v>
+      </c>
+      <c r="D6155">
+        <v>0</v>
+      </c>
+      <c r="E6155">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6156">
+      <c r="A6156" s="2">
+        <v>46234</v>
+      </c>
+      <c r="B6156">
+        <v>880</v>
+      </c>
+      <c r="C6156">
+        <v>0</v>
+      </c>
+      <c r="D6156">
+        <v>0</v>
+      </c>
+      <c r="E6156">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6157">
+      <c r="A6157" s="2">
+        <v>46234</v>
+      </c>
+      <c r="B6157">
+        <v>880</v>
+      </c>
+      <c r="C6157">
+        <v>0</v>
+      </c>
+      <c r="D6157">
+        <v>0</v>
+      </c>
+      <c r="E6157">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6158">
+      <c r="A6158" s="2">
+        <v>46234</v>
+      </c>
+      <c r="B6158">
+        <v>880</v>
+      </c>
+      <c r="C6158">
+        <v>0</v>
+      </c>
+      <c r="D6158">
+        <v>0</v>
+      </c>
+      <c r="E6158">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6159">
+      <c r="A6159" s="2">
+        <v>46234</v>
+      </c>
+      <c r="B6159">
+        <v>880</v>
+      </c>
+      <c r="C6159">
+        <v>0</v>
+      </c>
+      <c r="D6159">
+        <v>0</v>
+      </c>
+      <c r="E6159">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6160">
+      <c r="A6160" s="2">
+        <v>46234</v>
+      </c>
+      <c r="B6160">
+        <v>880</v>
+      </c>
+      <c r="C6160">
+        <v>0</v>
+      </c>
+      <c r="D6160">
+        <v>0</v>
+      </c>
+      <c r="E6160">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6161">
+      <c r="A6161" s="2">
+        <v>46234</v>
+      </c>
+      <c r="B6161">
+        <v>880</v>
+      </c>
+      <c r="C6161">
+        <v>0</v>
+      </c>
+      <c r="D6161">
+        <v>0</v>
+      </c>
+      <c r="E6161">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data-raw/resultados_supersete.xlsx
+++ b/data-raw/resultados_supersete.xlsx
@@ -355,7 +355,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E6161"/>
+  <dimension ref="A1:E6168"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" style="2" customWidth="1"/>
@@ -105108,6 +105108,125 @@
         <v>7</v>
       </c>
     </row>
+    <row r="6162">
+      <c r="A6162" s="2">
+        <v>46237</v>
+      </c>
+      <c r="B6162">
+        <v>881</v>
+      </c>
+      <c r="C6162">
+        <v>0</v>
+      </c>
+      <c r="D6162">
+        <v>0</v>
+      </c>
+      <c r="E6162">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6163">
+      <c r="A6163" s="2">
+        <v>46237</v>
+      </c>
+      <c r="B6163">
+        <v>881</v>
+      </c>
+      <c r="C6163">
+        <v>0</v>
+      </c>
+      <c r="D6163">
+        <v>0</v>
+      </c>
+      <c r="E6163">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6164">
+      <c r="A6164" s="2">
+        <v>46237</v>
+      </c>
+      <c r="B6164">
+        <v>881</v>
+      </c>
+      <c r="C6164">
+        <v>0</v>
+      </c>
+      <c r="D6164">
+        <v>0</v>
+      </c>
+      <c r="E6164">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6165">
+      <c r="A6165" s="2">
+        <v>46237</v>
+      </c>
+      <c r="B6165">
+        <v>881</v>
+      </c>
+      <c r="C6165">
+        <v>0</v>
+      </c>
+      <c r="D6165">
+        <v>0</v>
+      </c>
+      <c r="E6165">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6166">
+      <c r="A6166" s="2">
+        <v>46237</v>
+      </c>
+      <c r="B6166">
+        <v>881</v>
+      </c>
+      <c r="C6166">
+        <v>0</v>
+      </c>
+      <c r="D6166">
+        <v>0</v>
+      </c>
+      <c r="E6166">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6167">
+      <c r="A6167" s="2">
+        <v>46237</v>
+      </c>
+      <c r="B6167">
+        <v>881</v>
+      </c>
+      <c r="C6167">
+        <v>0</v>
+      </c>
+      <c r="D6167">
+        <v>0</v>
+      </c>
+      <c r="E6167">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6168">
+      <c r="A6168" s="2">
+        <v>46237</v>
+      </c>
+      <c r="B6168">
+        <v>881</v>
+      </c>
+      <c r="C6168">
+        <v>0</v>
+      </c>
+      <c r="D6168">
+        <v>0</v>
+      </c>
+      <c r="E6168">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data-raw/resultados_supersete.xlsx
+++ b/data-raw/resultados_supersete.xlsx
@@ -375,7 +375,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E6175"/>
+  <dimension ref="A1:E6182"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" style="1" customWidth="1"/>
@@ -105356,6 +105356,125 @@
         <v>3</v>
       </c>
     </row>
+    <row r="6176" spans="1:5">
+      <c r="A6176" s="1">
+        <v>46241</v>
+      </c>
+      <c r="B6176">
+        <v>883</v>
+      </c>
+      <c r="C6176">
+        <v>0</v>
+      </c>
+      <c r="D6176">
+        <v>0</v>
+      </c>
+      <c r="E6176">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6177" spans="1:5">
+      <c r="A6177" s="1">
+        <v>46241</v>
+      </c>
+      <c r="B6177">
+        <v>883</v>
+      </c>
+      <c r="C6177">
+        <v>0</v>
+      </c>
+      <c r="D6177">
+        <v>0</v>
+      </c>
+      <c r="E6177">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6178" spans="1:5">
+      <c r="A6178" s="1">
+        <v>46241</v>
+      </c>
+      <c r="B6178">
+        <v>883</v>
+      </c>
+      <c r="C6178">
+        <v>0</v>
+      </c>
+      <c r="D6178">
+        <v>0</v>
+      </c>
+      <c r="E6178">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6179" spans="1:5">
+      <c r="A6179" s="1">
+        <v>46241</v>
+      </c>
+      <c r="B6179">
+        <v>883</v>
+      </c>
+      <c r="C6179">
+        <v>0</v>
+      </c>
+      <c r="D6179">
+        <v>0</v>
+      </c>
+      <c r="E6179">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6180" spans="1:5">
+      <c r="A6180" s="1">
+        <v>46241</v>
+      </c>
+      <c r="B6180">
+        <v>883</v>
+      </c>
+      <c r="C6180">
+        <v>0</v>
+      </c>
+      <c r="D6180">
+        <v>0</v>
+      </c>
+      <c r="E6180">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6181" spans="1:5">
+      <c r="A6181" s="1">
+        <v>46241</v>
+      </c>
+      <c r="B6181">
+        <v>883</v>
+      </c>
+      <c r="C6181">
+        <v>0</v>
+      </c>
+      <c r="D6181">
+        <v>0</v>
+      </c>
+      <c r="E6181">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6182" spans="1:5">
+      <c r="A6182" s="1">
+        <v>46241</v>
+      </c>
+      <c r="B6182">
+        <v>883</v>
+      </c>
+      <c r="C6182">
+        <v>0</v>
+      </c>
+      <c r="D6182">
+        <v>0</v>
+      </c>
+      <c r="E6182">
+        <v>5</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data-raw/resultados_supersete.xlsx
+++ b/data-raw/resultados_supersete.xlsx
@@ -375,7 +375,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E6182"/>
+  <dimension ref="A1:E6189"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" style="1" customWidth="1"/>
@@ -105475,6 +105475,125 @@
         <v>5</v>
       </c>
     </row>
+    <row r="6183" spans="1:5">
+      <c r="A6183" s="1">
+        <v>46244</v>
+      </c>
+      <c r="B6183">
+        <v>884</v>
+      </c>
+      <c r="C6183">
+        <v>0</v>
+      </c>
+      <c r="D6183">
+        <v>0</v>
+      </c>
+      <c r="E6183">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6184" spans="1:5">
+      <c r="A6184" s="1">
+        <v>46244</v>
+      </c>
+      <c r="B6184">
+        <v>884</v>
+      </c>
+      <c r="C6184">
+        <v>0</v>
+      </c>
+      <c r="D6184">
+        <v>0</v>
+      </c>
+      <c r="E6184">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6185" spans="1:5">
+      <c r="A6185" s="1">
+        <v>46244</v>
+      </c>
+      <c r="B6185">
+        <v>884</v>
+      </c>
+      <c r="C6185">
+        <v>0</v>
+      </c>
+      <c r="D6185">
+        <v>0</v>
+      </c>
+      <c r="E6185">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6186" spans="1:5">
+      <c r="A6186" s="1">
+        <v>46244</v>
+      </c>
+      <c r="B6186">
+        <v>884</v>
+      </c>
+      <c r="C6186">
+        <v>0</v>
+      </c>
+      <c r="D6186">
+        <v>0</v>
+      </c>
+      <c r="E6186">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6187" spans="1:5">
+      <c r="A6187" s="1">
+        <v>46244</v>
+      </c>
+      <c r="B6187">
+        <v>884</v>
+      </c>
+      <c r="C6187">
+        <v>0</v>
+      </c>
+      <c r="D6187">
+        <v>0</v>
+      </c>
+      <c r="E6187">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6188" spans="1:5">
+      <c r="A6188" s="1">
+        <v>46244</v>
+      </c>
+      <c r="B6188">
+        <v>884</v>
+      </c>
+      <c r="C6188">
+        <v>0</v>
+      </c>
+      <c r="D6188">
+        <v>0</v>
+      </c>
+      <c r="E6188">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6189" spans="1:5">
+      <c r="A6189" s="1">
+        <v>46244</v>
+      </c>
+      <c r="B6189">
+        <v>884</v>
+      </c>
+      <c r="C6189">
+        <v>0</v>
+      </c>
+      <c r="D6189">
+        <v>0</v>
+      </c>
+      <c r="E6189">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data-raw/resultados_supersete.xlsx
+++ b/data-raw/resultados_supersete.xlsx
@@ -375,7 +375,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E6189"/>
+  <dimension ref="A1:E6196"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" style="1" customWidth="1"/>
@@ -105594,6 +105594,125 @@
         <v>0</v>
       </c>
     </row>
+    <row r="6190" spans="1:5">
+      <c r="A6190" s="1">
+        <v>46246</v>
+      </c>
+      <c r="B6190">
+        <v>885</v>
+      </c>
+      <c r="C6190">
+        <v>0</v>
+      </c>
+      <c r="D6190">
+        <v>0</v>
+      </c>
+      <c r="E6190">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6191" spans="1:5">
+      <c r="A6191" s="1">
+        <v>46246</v>
+      </c>
+      <c r="B6191">
+        <v>885</v>
+      </c>
+      <c r="C6191">
+        <v>0</v>
+      </c>
+      <c r="D6191">
+        <v>0</v>
+      </c>
+      <c r="E6191">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6192" spans="1:5">
+      <c r="A6192" s="1">
+        <v>46246</v>
+      </c>
+      <c r="B6192">
+        <v>885</v>
+      </c>
+      <c r="C6192">
+        <v>0</v>
+      </c>
+      <c r="D6192">
+        <v>0</v>
+      </c>
+      <c r="E6192">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6193" spans="1:5">
+      <c r="A6193" s="1">
+        <v>46246</v>
+      </c>
+      <c r="B6193">
+        <v>885</v>
+      </c>
+      <c r="C6193">
+        <v>0</v>
+      </c>
+      <c r="D6193">
+        <v>0</v>
+      </c>
+      <c r="E6193">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6194" spans="1:5">
+      <c r="A6194" s="1">
+        <v>46246</v>
+      </c>
+      <c r="B6194">
+        <v>885</v>
+      </c>
+      <c r="C6194">
+        <v>0</v>
+      </c>
+      <c r="D6194">
+        <v>0</v>
+      </c>
+      <c r="E6194">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6195" spans="1:5">
+      <c r="A6195" s="1">
+        <v>46246</v>
+      </c>
+      <c r="B6195">
+        <v>885</v>
+      </c>
+      <c r="C6195">
+        <v>0</v>
+      </c>
+      <c r="D6195">
+        <v>0</v>
+      </c>
+      <c r="E6195">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6196" spans="1:5">
+      <c r="A6196" s="1">
+        <v>46246</v>
+      </c>
+      <c r="B6196">
+        <v>885</v>
+      </c>
+      <c r="C6196">
+        <v>0</v>
+      </c>
+      <c r="D6196">
+        <v>0</v>
+      </c>
+      <c r="E6196">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data-raw/resultados_supersete.xlsx
+++ b/data-raw/resultados_supersete.xlsx
@@ -375,7 +375,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E6196"/>
+  <dimension ref="A1:E6203"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" style="1" customWidth="1"/>
@@ -105713,6 +105713,125 @@
         <v>9</v>
       </c>
     </row>
+    <row r="6197" spans="1:5">
+      <c r="A6197" s="1">
+        <v>46248</v>
+      </c>
+      <c r="B6197">
+        <v>886</v>
+      </c>
+      <c r="C6197">
+        <v>0</v>
+      </c>
+      <c r="D6197">
+        <v>0</v>
+      </c>
+      <c r="E6197">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6198" spans="1:5">
+      <c r="A6198" s="1">
+        <v>46248</v>
+      </c>
+      <c r="B6198">
+        <v>886</v>
+      </c>
+      <c r="C6198">
+        <v>0</v>
+      </c>
+      <c r="D6198">
+        <v>0</v>
+      </c>
+      <c r="E6198">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6199" spans="1:5">
+      <c r="A6199" s="1">
+        <v>46248</v>
+      </c>
+      <c r="B6199">
+        <v>886</v>
+      </c>
+      <c r="C6199">
+        <v>0</v>
+      </c>
+      <c r="D6199">
+        <v>0</v>
+      </c>
+      <c r="E6199">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6200" spans="1:5">
+      <c r="A6200" s="1">
+        <v>46248</v>
+      </c>
+      <c r="B6200">
+        <v>886</v>
+      </c>
+      <c r="C6200">
+        <v>0</v>
+      </c>
+      <c r="D6200">
+        <v>0</v>
+      </c>
+      <c r="E6200">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6201" spans="1:5">
+      <c r="A6201" s="1">
+        <v>46248</v>
+      </c>
+      <c r="B6201">
+        <v>886</v>
+      </c>
+      <c r="C6201">
+        <v>0</v>
+      </c>
+      <c r="D6201">
+        <v>0</v>
+      </c>
+      <c r="E6201">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6202" spans="1:5">
+      <c r="A6202" s="1">
+        <v>46248</v>
+      </c>
+      <c r="B6202">
+        <v>886</v>
+      </c>
+      <c r="C6202">
+        <v>0</v>
+      </c>
+      <c r="D6202">
+        <v>0</v>
+      </c>
+      <c r="E6202">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6203" spans="1:5">
+      <c r="A6203" s="1">
+        <v>46248</v>
+      </c>
+      <c r="B6203">
+        <v>886</v>
+      </c>
+      <c r="C6203">
+        <v>0</v>
+      </c>
+      <c r="D6203">
+        <v>0</v>
+      </c>
+      <c r="E6203">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data-raw/resultados_supersete.xlsx
+++ b/data-raw/resultados_supersete.xlsx
@@ -375,7 +375,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E6203"/>
+  <dimension ref="A1:E6210"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" style="1" customWidth="1"/>
@@ -105832,6 +105832,125 @@
         <v>9</v>
       </c>
     </row>
+    <row r="6204" spans="1:5">
+      <c r="A6204" s="1">
+        <v>46251</v>
+      </c>
+      <c r="B6204">
+        <v>887</v>
+      </c>
+      <c r="C6204">
+        <v>0</v>
+      </c>
+      <c r="D6204">
+        <v>0</v>
+      </c>
+      <c r="E6204">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6205" spans="1:5">
+      <c r="A6205" s="1">
+        <v>46251</v>
+      </c>
+      <c r="B6205">
+        <v>887</v>
+      </c>
+      <c r="C6205">
+        <v>0</v>
+      </c>
+      <c r="D6205">
+        <v>0</v>
+      </c>
+      <c r="E6205">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6206" spans="1:5">
+      <c r="A6206" s="1">
+        <v>46251</v>
+      </c>
+      <c r="B6206">
+        <v>887</v>
+      </c>
+      <c r="C6206">
+        <v>0</v>
+      </c>
+      <c r="D6206">
+        <v>0</v>
+      </c>
+      <c r="E6206">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6207" spans="1:5">
+      <c r="A6207" s="1">
+        <v>46251</v>
+      </c>
+      <c r="B6207">
+        <v>887</v>
+      </c>
+      <c r="C6207">
+        <v>0</v>
+      </c>
+      <c r="D6207">
+        <v>0</v>
+      </c>
+      <c r="E6207">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6208" spans="1:5">
+      <c r="A6208" s="1">
+        <v>46251</v>
+      </c>
+      <c r="B6208">
+        <v>887</v>
+      </c>
+      <c r="C6208">
+        <v>0</v>
+      </c>
+      <c r="D6208">
+        <v>0</v>
+      </c>
+      <c r="E6208">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6209" spans="1:5">
+      <c r="A6209" s="1">
+        <v>46251</v>
+      </c>
+      <c r="B6209">
+        <v>887</v>
+      </c>
+      <c r="C6209">
+        <v>0</v>
+      </c>
+      <c r="D6209">
+        <v>0</v>
+      </c>
+      <c r="E6209">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6210" spans="1:5">
+      <c r="A6210" s="1">
+        <v>46251</v>
+      </c>
+      <c r="B6210">
+        <v>887</v>
+      </c>
+      <c r="C6210">
+        <v>0</v>
+      </c>
+      <c r="D6210">
+        <v>0</v>
+      </c>
+      <c r="E6210">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data-raw/resultados_supersete.xlsx
+++ b/data-raw/resultados_supersete.xlsx
@@ -375,7 +375,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E6210"/>
+  <dimension ref="A1:E6217"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" style="1" customWidth="1"/>
@@ -105951,6 +105951,125 @@
         <v>9</v>
       </c>
     </row>
+    <row r="6211" spans="1:5">
+      <c r="A6211" s="1">
+        <v>46253</v>
+      </c>
+      <c r="B6211">
+        <v>888</v>
+      </c>
+      <c r="C6211">
+        <v>0</v>
+      </c>
+      <c r="D6211">
+        <v>0</v>
+      </c>
+      <c r="E6211">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6212" spans="1:5">
+      <c r="A6212" s="1">
+        <v>46253</v>
+      </c>
+      <c r="B6212">
+        <v>888</v>
+      </c>
+      <c r="C6212">
+        <v>0</v>
+      </c>
+      <c r="D6212">
+        <v>0</v>
+      </c>
+      <c r="E6212">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6213" spans="1:5">
+      <c r="A6213" s="1">
+        <v>46253</v>
+      </c>
+      <c r="B6213">
+        <v>888</v>
+      </c>
+      <c r="C6213">
+        <v>0</v>
+      </c>
+      <c r="D6213">
+        <v>0</v>
+      </c>
+      <c r="E6213">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6214" spans="1:5">
+      <c r="A6214" s="1">
+        <v>46253</v>
+      </c>
+      <c r="B6214">
+        <v>888</v>
+      </c>
+      <c r="C6214">
+        <v>0</v>
+      </c>
+      <c r="D6214">
+        <v>0</v>
+      </c>
+      <c r="E6214">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6215" spans="1:5">
+      <c r="A6215" s="1">
+        <v>46253</v>
+      </c>
+      <c r="B6215">
+        <v>888</v>
+      </c>
+      <c r="C6215">
+        <v>0</v>
+      </c>
+      <c r="D6215">
+        <v>0</v>
+      </c>
+      <c r="E6215">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6216" spans="1:5">
+      <c r="A6216" s="1">
+        <v>46253</v>
+      </c>
+      <c r="B6216">
+        <v>888</v>
+      </c>
+      <c r="C6216">
+        <v>0</v>
+      </c>
+      <c r="D6216">
+        <v>0</v>
+      </c>
+      <c r="E6216">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6217" spans="1:5">
+      <c r="A6217" s="1">
+        <v>46253</v>
+      </c>
+      <c r="B6217">
+        <v>888</v>
+      </c>
+      <c r="C6217">
+        <v>0</v>
+      </c>
+      <c r="D6217">
+        <v>0</v>
+      </c>
+      <c r="E6217">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data-raw/resultados_supersete.xlsx
+++ b/data-raw/resultados_supersete.xlsx
@@ -375,7 +375,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E6217"/>
+  <dimension ref="A1:E6224"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" style="1" customWidth="1"/>
@@ -106070,6 +106070,125 @@
         <v>0</v>
       </c>
     </row>
+    <row r="6218" spans="1:5">
+      <c r="A6218" s="1">
+        <v>46255</v>
+      </c>
+      <c r="B6218">
+        <v>889</v>
+      </c>
+      <c r="C6218">
+        <v>0</v>
+      </c>
+      <c r="D6218">
+        <v>0</v>
+      </c>
+      <c r="E6218">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6219" spans="1:5">
+      <c r="A6219" s="1">
+        <v>46255</v>
+      </c>
+      <c r="B6219">
+        <v>889</v>
+      </c>
+      <c r="C6219">
+        <v>0</v>
+      </c>
+      <c r="D6219">
+        <v>0</v>
+      </c>
+      <c r="E6219">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6220" spans="1:5">
+      <c r="A6220" s="1">
+        <v>46255</v>
+      </c>
+      <c r="B6220">
+        <v>889</v>
+      </c>
+      <c r="C6220">
+        <v>0</v>
+      </c>
+      <c r="D6220">
+        <v>0</v>
+      </c>
+      <c r="E6220">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6221" spans="1:5">
+      <c r="A6221" s="1">
+        <v>46255</v>
+      </c>
+      <c r="B6221">
+        <v>889</v>
+      </c>
+      <c r="C6221">
+        <v>0</v>
+      </c>
+      <c r="D6221">
+        <v>0</v>
+      </c>
+      <c r="E6221">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6222" spans="1:5">
+      <c r="A6222" s="1">
+        <v>46255</v>
+      </c>
+      <c r="B6222">
+        <v>889</v>
+      </c>
+      <c r="C6222">
+        <v>0</v>
+      </c>
+      <c r="D6222">
+        <v>0</v>
+      </c>
+      <c r="E6222">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6223" spans="1:5">
+      <c r="A6223" s="1">
+        <v>46255</v>
+      </c>
+      <c r="B6223">
+        <v>889</v>
+      </c>
+      <c r="C6223">
+        <v>0</v>
+      </c>
+      <c r="D6223">
+        <v>0</v>
+      </c>
+      <c r="E6223">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6224" spans="1:5">
+      <c r="A6224" s="1">
+        <v>46255</v>
+      </c>
+      <c r="B6224">
+        <v>889</v>
+      </c>
+      <c r="C6224">
+        <v>0</v>
+      </c>
+      <c r="D6224">
+        <v>0</v>
+      </c>
+      <c r="E6224">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
